--- a/tools/importer/reports/import-neuwagen-model.report.xlsx
+++ b/tools/importer/reports/import-neuwagen-model.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
   <si>
     <t>_reportFile</t>
   </si>
@@ -49,7 +49,7 @@
     <t>["cards-teaser","columns-media-text","cards-image-overlay"]</t>
   </si>
   <si>
-    <t/>
+    <t>{"1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:766808f7-b740-4399-80bf-30c6ffcf90aa/original/as/1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg","1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a5928a7f-6ff6-4cec-aa89-3ebfd56b1609/original/as/1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg","1920x1080_A5_E_2024_7736_no_Cast-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6e40c173-687b-420c-a20f-474609741022/original/as/1920x1080_A5_E_2024_7736_no_Cast-(original).jpg","1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ce866967-bdef-4fa5-ad0d-6c6fde16ff41/original/as/1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg","1920x1080_bidi_stillbild-animation.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:18e2fed5-17fb-49d8-a39d-697aa73e885b/original/as/1920x1080_bidi_stillbild-animation.jpg","1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d51bd1ea-e5a8-47c8-970b-16f65de1e030/original/as/1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg","1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:66a5ab2a-8920-42e3-b8cf-d3059ad85ba5/original/as/1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1080_qdiv_p_181005_rgb-12566-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d858a757-a888-4f13-b141-c05a9f9ef159/original/as/1920x1080_qdiv_p_181005_rgb-12566-(original).jpg","1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cf02c1c0-8469-4fef-a7ad-939512052326/original/as/1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg","1920x1080_ADM_as_2025_7853.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a899808d-433d-479b-a5b4-f01935209dfd/original/as/1920x1080_ADM_as_2025_7853.jpg","1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e2c42a97-8d7f-4a9d-8382-56708bb3c827/original/as/1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:65cf45f4-383f-4163-ab61-d0b87a001473/original/as/1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg","1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e5e312d9-7fe7-4a92-a404-157135a5ae3d/original/as/1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg","1920x1080_Q4_r_2022_4070_1-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e75bb944-4c7f-4f89-98f2-6db62d0e9dd3/original/as/1920x1080_Q4_r_2022_4070_1-(original).jpg"}</t>
   </si>
   <si>
     <t>de/elektromobilitaet</t>
@@ -61,7 +61,7 @@
     <t>elektromobilitaet</t>
   </si>
   <si>
-    <t>2026-10-26T18:05:41.040Z</t>
+    <t>2026-10-27T12:51:03.082Z</t>
   </si>
   <si>
     <t>E-Mobilität im Alltag | Audi Deutschland</t>
@@ -70,6 +70,15 @@
     <t>https://www.audi.de/de/elektromobilitaet/</t>
   </si>
   <si>
+    <t>language-masters/de/elektromobilitaet.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/elektromobilitaet</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:25.440Z</t>
+  </si>
+  <si>
     <t>de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
   </si>
   <si>
@@ -236,6 +245,87 @@
   </si>
   <si>
     <t>https://www.audi.de/de/neuwagen/q5/q5-suv/</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2-e-tron/a2-e-tron</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:51.264Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-allstreet.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-allstreet</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:37.760Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-limousine.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-limousine</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:33.161Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:42.461Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3/a3-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:47.307Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:22:09.364Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-sportback</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:22:04.513Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:22:00.558Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5/q5-suv</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:21:56.358Z</t>
   </si>
 </sst>
 </file>
@@ -624,12 +714,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
@@ -704,287 +794,607 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="J6" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="J7" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="I8" t="s">
         <v>52</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="J8" t="s">
         <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="I9" t="s">
         <v>58</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="J9" t="s">
         <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="I10" t="s">
         <v>64</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="J10" t="s">
         <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="I11" t="s">
         <v>70</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="J11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>72</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="J11" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-neuwagen-model.report.xlsx
+++ b/tools/importer/reports/import-neuwagen-model.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="216">
   <si>
     <t>_reportFile</t>
   </si>
@@ -22,6 +22,12 @@
     <t>damAssets</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>livechatWidgetsRemoved</t>
   </si>
   <si>
@@ -52,6 +58,9 @@
     <t>{"1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:766808f7-b740-4399-80bf-30c6ffcf90aa/original/as/1920x1080_E-Vorteile_Q6_SB_2023_5285_01.jpg","1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a5928a7f-6ff6-4cec-aa89-3ebfd56b1609/original/as/1920x1080_E-Fahrzeuge_A6e_2023_6017_01.jpg","1920x1080_A5_E_2024_7736_no_Cast-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:6e40c173-687b-420c-a20f-474609741022/original/as/1920x1080_A5_E_2024_7736_no_Cast-(original).jpg","1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:ce866967-bdef-4fa5-ad0d-6c6fde16ff41/original/as/1920x1080_Laden_sq6_2023_5304-cast-36346113_01.jpg","1920x1080_bidi_stillbild-animation.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:18e2fed5-17fb-49d8-a39d-697aa73e885b/original/as/1920x1080_bidi_stillbild-animation.jpg","1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d51bd1ea-e5a8-47c8-970b-16f65de1e030/original/as/1920x1080_E-Foerderung_A3_2023_5821_Cast.jpg","1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:66a5ab2a-8920-42e3-b8cf-d3059ad85ba5/original/as/1920x1080_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1080_qdiv_p_181005_rgb-12566-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:d858a757-a888-4f13-b141-c05a9f9ef159/original/as/1920x1080_qdiv_p_181005_rgb-12566-(original).jpg","1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cf02c1c0-8469-4fef-a7ad-939512052326/original/as/1920x1080_Zubehoer_A6e_as_2023_6023_roof_box_closed_1_01.jpg","1920x1080_ADM_as_2025_7853.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:a899808d-433d-479b-a5b4-f01935209dfd/original/as/1920x1080_ADM_as_2025_7853.jpg","1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e2c42a97-8d7f-4a9d-8382-56708bb3c827/original/as/1920x1920_e-mob_reichweite_A6e_2023_5921_2_02.jpg","1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:65cf45f4-383f-4163-ab61-d0b87a001473/original/as/1920x1920_Ladezeit_A6e_2023_6002_1_01.jpg","1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e5e312d9-7fe7-4a92-a404-157135a5ae3d/original/as/1920x1920_Ladekarte_Q6_SB_2023_5214_withoutcast_1_01.jpg","1920x1080_Q4_r_2022_4070_1-original.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e75bb944-4c7f-4f89-98f2-6db62d0e9dd3/original/as/1920x1080_Q4_r_2022_4070_1-(original).jpg"}</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>de/elektromobilitaet</t>
   </si>
   <si>
@@ -70,6 +79,53 @@
     <t>https://www.audi.de/de/elektromobilitaet/</t>
   </si>
   <si>
+    <t>de/neuwagen.report.json</t>
+  </si>
+  <si>
+    <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
+    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:665:13)
+    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:957:22)</t>
+  </si>
+  <si>
+    <t>de/neuwagen</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:19:55.089Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?excat-fragment=model-filter</t>
+  </si>
+  <si>
+    <t>language-masters/de.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","carline-slider","carousel-cards","cards-image-overlay","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>{"9x16_Leasingangebote_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:cedff9d8-f4ae-413a-aae8-0f081db8260c/original/as/9x16_Leasingangebote_01.jpg","cards/audi-a2-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbdRSH_37Zdre57syy0006TZadSVhH0k4uZjeVgCkqVKFWe_PykE6S2c3UTTZMJjFVoVgURFsQqfUGWltB0K0ofbBSKaLimyIoKEXQ9klwRanQegFx4svHOYfzO_w4nLP2q9jQdwUP71z7Y_OfGyf2_YQQw64QgZ0i0O0s3ySEaLLJaVvL9nY_3zxr5bL20Mtag-72vJlfyFb3F3LDbM7cnbVWVrLVfEyM-xqxwVci-xiL-IiqPiaOif85mnlqhDdHOfmA3z30gwdHOhGd6rsrXcu12ttcu9dd7fScgS3N22WrbOVz5aJdr9cXF0v1smUu1QvlJdMsFXNmwS6Um43GrQ3ZH_GOCDTtvpg8XK_1nKZdyxVNc1gyc2Jjq9GxHFeMjZxjPMvWK0w_j7IX5SWU8xhPEf-XRJXESRJrJC5gHEB9ldQ5UhdJfY3xHHPX0cA4jnYY7TfSf5N5gUwdcTvGLsIu4deIvE1MIbbAzJNs-QK1g1ondRvpXaRvIOKIB5A-Rp5i-iRKkcQSqow6ix5AN9Avk_6A4DjBtwiXiBYxHkc6iryKfAbjPuKPEL-GHkN_A_1L0iVCdxO6jrSOcpbIe0QuIe1AqiF9hvQV8r3IfaZPEP8IdTfzt5C8TPIGyX9ITZCaJDWL8RBzv6Al0E6heWiX0Pej_05aJq2T_pHIaSLniXWY_JCbTxNbZKbHzCsYh4ifIXGQxEUS36A2SH5C8lNi3zP_NMozGMeYu0L6c8Q44ijGnWy6SvB-gm2CrxM8S_AHQocIHSF0lXCYsO__BJFviUaI3kP0INEu0ePEqhjvE3-RLV3Ud0ntIDVg7i-0eaS7kCPE_c0cwdiK9jPRdWLrSGNIL2M8gfIYynf-aSzbnYHjrnbadser7PX6TWc186jT9FqVolkuZVq2s9zyKgVzIZ-xVrotq-K5fTvTsNq2a1WqB_bk76hVa4WaaZoZq-N_hef4B1rJtG3PalqeNbDdnl-p5KcCfvN_25OpJF0DAAA.png","cards/audi-a3.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf37Sbm16c9N7S--SNCSSe28oldibP23aaXQd4sMQlc46RCH7tbltU5o_pjcxVQRfxL1MfHD-mYhSB0O3iaKIsLHNfwMZm4IPSl8se1FZVXDgJiJ668uHcw7ne87hcM7pX0VvuyV4fP_pG3tu7ep7ZAshuk0hAsdEoFlfuk0IUaG_WpNL7rjv77FlPuN2vYzsNMdzTq6YkfmmzDxQzczM5ae6mal1JyNXV8Nity8Uvb6cuI-efh_qAR99afE_dwpv7OCrHZ9swM_u-sZjOzqhDrVbq03ZkrU7W-5as1Ffq3ZcbXSqMF-UE9Pu4qKzODE1n5XTrnQL85N5N5vP5hcmnEJ-olJcmNf9El-KQMVti8GV-fJateKWswXH6U46WbFrar0j6wuiZ2d8kreIX2P4JYyDGB9gfETkBtG7iY0RmyH2MrH3iH3KyL_Ej5M8Q_IsyW9JbZL6A1NgrmD-jv0P6XHSDyL2ETyP0iJ0EvVewgaRZ4mcYeQS8QZxSfwoY1Wsq9g3EVFEDn-92jm0y-igDzH8NsZdxBaJ61hjWJvYHxLsJXgCpYhyD2oBzUNfRT-FYRCtEL1M9Ddi21hhrBRWAauM9RbWFez9DBxg4E-Uj9Hvx3gH4xKhrwl9grqBthetjPYF2lX0NPok-kPoHsNHiZ4lPsvoHSQ2Sdwk8TfJHpKDJG8ndR0zgvkKpod5DmsO6ydsHdvC_hHlEMoJQq8S-oVwnfAbDM4xuMXYBcxpIh6R40S-Yeww0Q1ifpcFEhdJfI55AUUj_ANDRYaXMY5gXCTyBJEVIs-TrJHawi5jP4n9OvZniN2IZ-jfJjhLsEbwOgOHGVhn4BqKgvIuyvuEXiT0Heoh1Abqc6gvEJ4h7LNL9E1GmsRPkThPci_JDqm_MEfR9hGdJbpOXMG8gvkz9hGUAMoI6jHUbcLbaH1or2E8jfG9f2hLbr1TbTXqNbfulQ567Uq1kX6qWvGWSwVnejK97FaXlr1S3inm0nK1uSxLXqvtphdkzW3J0syjD-fuK8-U82XHcdKy7j-aV_XPvZSuuZ6sSE923NaaHynlhgJ-8n8dZGj4sAMAAA.png","cards/audi-a5.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59Nmmazs5uZkMnudNyVndklpKyd_cmmqa4YlVx40YppKuLF9iQz7m6S3Syb2TSSXnhT9cYfsPhTlUJtb7QopVKsLf5bCmJBvbCooO2VYkRQaSoiOPHiPJz38L3fdw6858xvorfbETx675k_R25t33HgJ4RYawsROi5C7VZtmxDCpb_RlDVvd6BHbDme89b8nFxt7y44hYlcoKdmS85abs_herAWc3JpKSb6Ap_oDdzbTgXoGQwQfS3Ajrz4n1t9n9zClS2NEwqq14LNI1s-ER3qdpbasiObd3S8lfZya6Wx6qmj5cmSnHdLXn6uLKXn7ilPFCeLjisdKR23UJ4syrzjlvNlLWhxWYRcrysGF-aqKw3Xq-ZLjrNWdvJi-2PdgmzXRM_W7UmPc9t1hp9Hn0E_R_wWibswxjCmMI5hvInxHqkcqdOkLpL6ivQ10n9gCawFrN_JjpAtkl1E3ENYIXyU8AdEOsR04uvE32HnZcwW5hzmM4w1SN2J_QL2VTKbiALqJbQhho-hT6AHE2uYGuYodgh7DPs7MmcJ9xE-ReRuoiVUH62F9jn6LhKLJL4g8RfGBlY_dgw7jV3FPkEmz8ADDNwk8i5aHG0a_Q2Ut1EuoJxHuYm6F7WKKlE_Rb2KlkUbR9uP1iVxEXMf5hFGd5H8nuQmyX9I_kuqh9Qg6Sukf8UysF7E8rEuYc9ib5LRyNhk9pP5kchJlJdQzqH8QqxF7FUGZxm8gLGONUl8hfhxxg6ROInxMMZ5jPcx50l-RPITrA-JaMSuMXSD4Tr60-gfM_Ic8QXiR8lUybxC5rMgoog-xBH6NwjfR3iGcJPwDwwcYmCdgRtEIkSC9z6L8g1RhahJ9AliU8QOEHuK2An0aRKvY1xnZxvzLcyvSe0ldZDUKum_sUZRp9EUEg-ReBwzgvUl1s9EQkRuJ7pBbAO1F_Vl9HX0b4O41bzWaqOz3Gp6Lb8y43fdxnL2cMP165WSM1nO1r1Gre5Xis5EISuX2nVZ8TtdLzsvm15HVqYOPli4vzpVLVYdx8nKVvDb_EYQ-kq26fnSlb5c9TorwUmlMBQKiv8DYOrdkbUDAAA.png","cards/audi-a6.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAA_1vzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grz9Wu1QZ56rnMhy1ePSvpKdrvVd7gyMAK1MXYByRYGIEE3z8gwWHDACZB5oEN3QniMxkyMzCwVgAZkQwgwMdXWpRTkFiUmKtXnplSkiGoYUAkEGZ3cQ1x9PQJBgCLqOBV6QAAAA.png","cards/audi-a6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcBRDHN79rPrrZu81uyOb2ut5pdveMkbN730nlxCsSS5FWiaaID9dNbnN3MXc5LntnpBVUKPiiKIIWoURK6YMGixSK1KKtXxQFH-xLLT60FaFiRFBoFVHc-PJjZpj5DzPMbP4q9Hc7As_s3fxj_M-BoSevIwjrbUEInRBC7VatTxCEKjsbTbfm7Q788Sm3kPLW_ZTba-_OOJliqlzw_M5qq9xzW36q_FQ-vZ6azZdT7sqKLAwG1UJ_oNF3IMCOwQCRcwGGDgn_c1v9hW1c2vZxQkH2emA8vV0nREa7nZW223GbD3S8tfZqa63R85TJ6aWiU83PLC1OZ2fcpXRmKVtYKGa8fCGbzhRzmYVc2ssWpxc9NZD4UghVva4wsrxQWWtUvUo65zjrBSctDNTqeXfBFXZsz8A9j3HXDcZeR5tDexvtLLqI_i-xMrE3iG0S-wjjOIkUifdIfEziChNXmbiNCaaIuYz5G8kEyf0IDyOGEMOIx5A6SBvIGtEjRM-w6yuMFsYCxqtMNUg8iPUm9j7sOwgZlAuoo4ydQSuiBX1rGCrGJMY-rBDWFNY17A8RBxFPId2LVEB6iEgOdRX1AloI_Vn0b9B_x5KxbKw8VgVrA-tr7BzDexm-jbKFGkWdRTtN-APC5wmfI3ISRULZg1JBcVE-R_kW9SBqF_0ixgGMo0zeT_wa8TvE_yb-D4khEiNMXGbiF8wY5luYPuYnWPNYt7BVbB17P_ZB7OtIpwi_S_gs4Z-RW4y8jDlDdI3oO0wdRj9J7BCx8xhV4heJf0b8J8xPkRTkq0yFGKujvYJ2ifE-ostEj2FXsL9AGEQ4ys6biI8iziE2EX9g-DDDRxi-iSQhTSMFM75G-AqRMJEXkcvI88gvIW9w32W0WfQTxG6wq43xPsZ3JPaQ6DHxF-YkyiyqjP4E-vMYEuYtpAGku4lsIW-h9KMcRwlW9yPa98Gt1bxWrxF8QtNr-aU5v1ttrCafa1T9einnzBSSda9Rq_ulrFPMJN2Vdt0t-Z2ul1x0m17HLZXnH888UilXshXHcZJuK3g4vxFcfCnZ9Hy36vpuz-usBZFSZjQUJP8HmeY5vLgDAAA.png","cards/audi-q3.png":"https://mediaservice.audi.com/media/fast/v3_x2TW2gcdRSH__22adrN7mxmQqY7kzEjmd0xiayZvWQ3qSwYKRH6ULUxVVHYTrKzyYbsZt3Mxpj6oILYlxYfWqsVaUl9sValREOhRaXRIgoqIiit4OXJS0TESxUfdOLLxzmH8zsXOOf8z6Kt1RQ8dOf533b_tWPnfd8gxHJDiNCqCDXqM9uEEGV2VWvujDcU-LvtR7Ipb9lPuUuNoYyTKaTGJrPZfGo8m0658_Ope7MTkwdT---KifZAKdoC_bbrAUI_BZBCAXY2xf_cqry6hdNbPk4oyF4OjAe3dELqajXnG27Trd3W9BYbC_XF6pIn9-enC-VCrpAv5Nx0biSbH3GGR0eGc9NuJjc65Xjl0dzUcMXzRpSgxAciVPZaonNuqrRYLXuldM5xlvNOWuyozE25KzNi-9b8DJzjpgrdz6JOoJ5EXWPgJNpb6IPoY-jH0c-hX6TnX4xTmCnM1zAvYX5K3zX6_sASWBWsX7B17CHsfYg7CEcJv02kibSXmEr8SeJv0HMVo44xhXGUwSrm7SQ-IXkDoSEyiAeQLyN_iNKG0kX3cdQCegVDwegnESIxSOIayQuE2wm_TKSAlENeQamjrKOqaGW0j9B-JxEjsULiNIk1kmk69tHxJ5E3UcZRz6JeJfo60StE15FWkdPIe5BLyBeRN5A_RrFR8ih3o7ToPop2CWM_xmH6b6X3Or036P0HcztmJ-bN9P2KpWM9h-VjXcZ6n8QkAxdIKiQ1kl8TPUN0jegPxOrEXqRzks4NBs4QGyG-SPwUg4fQVtHvR19HD3qV6b2C9Q6xL1G-petHumdRj6C-y8AG8TniT2NWMJ8iWSL5Asn3EO2Ix9m1SfgA4Rrh04TPEv6KjkN0HKbjOyIRIq8QCbY-RvRzpCjSw0g-0hNIx4iNEXsG7SV6GhivYnyGuQdzib6_sfqRx1GiaAfQHsOIYH1P8giRENIJpE1im8htyM9zywnUL4Kjm_HqS9XmQr3m1f3ihN8qVxfsR6tlf7aYc0bz9qxXnZn1i1mnkLHd-casW_SbLc-edmte0y2OHbwns7c0VsqWHMex3XrwdX41OP2iXfN8t-z67pLXXAwixUxXKEj-D7iZcKa9AwAA.png","cards/audi-q4-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbZRiG_z5xu9scJjuzbHYnO2ZKJgnr2Ngkm002lYCpB2hBtK0tniBOkkk2ZZNNZydxoVrwSlEKVfCMrIjsha2HpSCFSlmseCMekAWlN9q9EMWKoNB6QHHizcP3_nzvx8fP-537RYz0HcEj-8_9PvXHzrEHvkeI1Z4QPkf4et3WDiFEg13tjtWy93p6KnUin7ZX3bQ16O3NZXLF9CFPu85yN105OpctpBdKVtpaWgqLUc8pRjz_jjc8-NY8SHs8jJXF_xxOfn6ItaEm6_O6V73ioaFPSBN9Z6lnOVbnNsde6S13V9oDW57N1edzuVKzUFtoWtZ8bq5YLxXtUq1uFbJ2MZ9tFoqFYqlWyCjeiAvC17D7Yvx4rbrSbtjVbD6TWS1ksmJnM9-yFjvipuH-7L4TbZvJM0SOEHmZyHlUGfVfohWizxJ9h-gFzGNor6G_i34R_SviV4hfxwBDwjiO8SvJv0i9QKqOuAfzAP4QQYfg64TWCUcIF5l-iun3mfkUrYtWQ7-dxJckD5C8gVAROcSDyB-hTDC5QSRPtImmoM2S8JEwSVwhuYF_FP_bSHnMe5G7KD2UdcxDqA3Uz1B_IxEmMU9ijcTnJAsE9hO4TmSd0CWkt5D3IVeRLeTLyF-g3IfiMnkadRPtMNqTaJeZvZXYNrEbxP4m9g_6GPo4-m70M5gPE_8ZI4rxEoaLcYnEUW7ZIKmQVEl-R-hNQucJ_US4y_iHRE8SXmB6wPSrqOtELxLdQmsQ2yT2McYmQYXwtyhXMfcQeYbIJlNb6KeIXyVZJfkJYhTxBObd7NrGfxj_CQI-Ao8ROElgm2AQ8yDB9widJrSFFEJ6FKmH9BzhCuYHhJ9GfZGZHtpZtK_R96H3iP-JMYt8B0oI1fu6U5g3Y_xIcAbpGuFryCPIryD_QOQbL0Qtuztoe-nu2F23fMTtN9rLqcfbDXexnM-UCqlFu91adMtzmWIuZS31Fq2y6_TtVN3q2I5Vrhy7P3dXtVKdq2YymZTV9a7IbXtRLqc6tms1LNca2M6K91LOTfi85v8AtYt2u40DAAA.png","cards/audi-q5.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSk_IztUhB2olJGHYTn3jH02vseip-3cZHh4ynHf3yc3_GdgBZrDOB1IMJ8FEvwMQIJjPYQE2VADIiaC-EyGzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggHJwayh4wAAAA.png","cards/audi-q6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbZRzHn32ytV1ySXpXd81lZzJyd7FW4i5Z_qyTiJlSRcQpdRPxRXZpLmlqk2bJpXbUF74ZE2GgKDIEmXT6RosiA5Epbk6RoSDi3mjxxTpRJlYEhU0RxatvPjzfH7_v73l-8H3WfhU7Bj3BkwfX_hj_c2jksasIsdwVInBSBLqd5jYhRJ2drbbTdPf6ejztFDPuspdxlrp7c3aulDnma6-32MlUDuezy5lGoZ9xFhaiYth3ih2-f9uQj8CGj8hbPkZ-Ev9za_LxLTy_pbEDfveyf3hiyyciY4PeQtfpOe07e26_u9jpt5ZceaLounat6GYbDddxC7PZUqM-lSvUCo1sPZfN5gu1UqHg5PY3FH_EBRGouwMxOl-r9lt1t5rN2_Zy0c6KoWaj5mQdsX3r_ey5l1s32PUC6gzqObQQ2r_EK8RfJL5G_AP00yQzJN8k-SHJK6TWSd3AACOIMY_xG-kk6YcQ9xAMEAwTPIHUQzpDVCW2Quxddn-O3kGvoZ9iskXyLsyXML_GegDrJiKH_BHKGLteRi2h-lc30RX0CcwA5iTmOtZ7BIcJvoF0G1IR6W4ieZQ2ynnUANpTaF-i_Y4ZxUxhVjHPYH6BlSd0kNAN5E2UGMo06lnC7xC-RPh95APIVWQH-VPkr1AOoQzQLqI_jL7CxB0k1kncJPE3iX9IjpAcJXWZ1C8YcYxXMDyMjzEPY17HUrA0rAexDmFdRVol_Drhc4R_Jtph9BjGFLE-sVeZPIq2Svxx4ufR6yQukrhE4keMC0gK0W-5ZRb1OdRPGB8jNk_sBFYV6zPEMOIZdl4jeD_BGYJtgt8TOkpohdA1JAlpP5K_2inCV4iEiehEniVaIXqE6Eluv4w6jfYa8Q12d9HfRv-G5AFSf2FMIE-jhNEeRTuOLmFcRxpC2kNkk-gm8nbk08iryD-gfucnq-l2llp-5NtuxyvPeIN6azH9dKvuzZXz9lQxPee2mnNeeZ9dyqWdhe6cU_Z6Azc967TdnlOuHHkkd1-1Ut1XtW077XT8r-W1_HyX023Xc-qO5yy5vb5fKefGAn7zf7KBWguiAwAA.png","cards/audi-q7.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoTk_IztUhB2olJGH4Wdzv6Sh50eFh52zTiU5L5xc0nYhn4EVaA6jOJBgjgASfEeABEcnA5gE2ZABIvJBfCZjZgYG1gogI5IBBPj4SotyChKLEnP1UlKTStMFNQyIBMLsLq4hjp4-wQBRTCXI4wAAAA.png","cards/audi-q8.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcdRiGf3m2SdvNzG5m4k53N0MGd2a2IZJmdpPmn11pahERtNLWFvGwmWRnk02zk83ubJraKnoQvFQvxaJCe1AiaBWCImKLtBYaghiqHpSe1IuK6cWiNeSgk14evhfe7-U9fN-Vu6K1WRe8cOjKvT3_tu06_jNCLNWEiKyISM2fbhFClNhdqbrTXn-o9-gLI33eUtDnLtb6805-uG9hpOb2DVbLfe7cXFzsDP2iNdxqORAicj1E7EaIXSviAR_kbePctiYXCd1L4fD89p6IdTbrczW37lb31b1Gbd5vVBY9pWfUy40MDU9NjXiT3vDkaHl_bsDxyrncaFggP-KW97vuwECp7KhhxJqIlLym6JidLDYqJa-YG3ScpSEnJ9oGq4EzmRc7tlvz8Brd_WjH0D4lZZM6QLqX9DjpC6Q_JP0FRj_GMsZVjHWM78jcJvM35gTmX2RlsofJ-oiDSHXkZeIaiSbJl-m6he6jT6Cfp7dC5g-sd7DWse8j9hF9FOVNlGuonSQuoA2TnkXvRN-L_iRWBKsX6w52Avsk9grRVqLvI-1FGkJ6DDkgNojyNMqLqPOoqyS2SL5Hyif1Dan7pDcw2zA3seJYJlYR6zLW19iP0_4U7f8gfYb6BNoy8m3kz5HvIm-hjKEUUVyUmyjrqD2oBdQjqM-hNkmcJ7WK_gz6l_Q8QvcdurcwdmB0YNhk_sR8CzPAvIZ5A_MW1gms_7BV7BT2EewNpA-QLyL_Rtwn_i4dx-m4h5nHHCXZJH0VSSH-Ew9tkphBex3tOskxkrMkX8M4hV3GXsB-G3sN0YLYiTjH7g2ih4geJVolukr7JO1naf8VSUb6COkT5AnkN5B_ICYT04m9Qnyc-KvEL9PRQ-oS6V_oqqF_jP493V9hjGGcxFgks4nZg3KQ1FFSZ9AlzG8xf0dqQ-oitkF8A6UV5SLaWbRLaDfRfgzv7iXPX6zU5_2q5weFY0GzVJnPnq6UgpnCoDM6lJ3xKtMzQWHAGc5n3bnajFsI6k0vO-VWvbpbGD_xbP5wcbw4UHQcJ-v64bsFlfD6C9nG1HwtdJw-5Z1peAtNz5_yCvls1Qvckhu4i169EfoK-c5IGPE_puUsMswDAAA.png","cards/audi-q9.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSU_IztUhB2olJGH4dPkY46s-6KbtFgT_-lEnzY4KnLkFAMryJzrQILZFUjw6wAJjnYGMAmSiQYRxSA-kxEzAwNrBZARyQACfHylRTkFiUWJuXopqUml6YIaBkQCYXYX1xBHT59gAGx0n1DjAAAA.png","cards/audi-e-tron-gt.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGH4XjRqu9uj7VdK8UFWr2dj9dMP95Rw8AKNIpxPpBg0QISfL-ABIcHA5gEWZIJIk6C-EwWzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggEPp39D5gAAAA.png","cards/audi-nuvolari.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjDEBjWe-dDzqpFyy9ofdnj-Hin56m76xmYGRjYGxgYWCwYQIBPuLQopyCxKDFXryi1uCA_rzizLFVQw4BIIMzu4hri6OkTDAD_J8cizwAAAA.png","cards/audi-f1.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjD0CK89NsGXslvP2aeuao66f8-K6u9DgzMDAzsDQwMLBYMIMAnXFqUU5BYlJirV5RaXJCfV5xZliqoYUAkEGZ3cQ1x9PQJBgBHdTswzwAAAA.png","1x1_Q9_2026_8802_withoutCast_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:78620da7-9245-4f73-8052-60256fa6cb25/original/as/1x1_Q9_2026_8802_withoutCast_02.jpg","A2e_2026_9667-S.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:c59f36c7-7701-4706-bede-958032bd6e86/original/as/A2e_2026_9667-S.jpg","1x1_Q7_ae_2026_8627_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:8766edf6-e8a7-4d3d-a428-e2629b9ba8ef/original/as/1x1_Q7_ae_2026_8627_02.jpg","1x1_Audi-driving-experience_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:47cb8339-8b41-44a6-9013-b42a1d4c56f0/original/as/1x1_Audi-driving-experience_01.jpg","1x1_Nuvolari_2026_9606_3_to_4_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:47beff9b-7bc4-4d7d-a0e0-eddef24a7c32/original/as/1x1_Nuvolari_2026_9606_3_to_4_01.jpg","1920x1920_RSeGTp_2024_6598_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:5aadf297-9332-40aa-ba6b-3eb9c4e8a7dc/original/as/1920x1920_RSeGTp_2024_6598_01.jpg","1920x1920_Gebrauchtwagen_q8_2023_5482-30724177_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:3ff1543f-0c38-431f-b69b-38bad983eeaf/original/as/1920x1920_Gebrauchtwagen_q8_2023_5482-30724177_02.jpg","1920x1920_Q5_2024_6816_1_V4_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0861f618-db68-43e0-b039-f658d1e08f7f/original/as/1920x1920_Q5_2024_6816_1_V4_02.jpg","1920x1920_Probefahrt_Q4e_2026_8409_DE_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:aab09321-0c1e-4fa0-9929-b51fe7f1140b/original/as/1920x1920_Probefahrt_Q4e_2026_8409_DE_02.jpg","1920x1920_exclusive_sq6_ascari_05_04.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e36deb3d-0460-4c5c-ac56-9ce8fb6ec047/original/as/1920x1920_exclusive_sq6_ascari_05_04.jpg","1920x1920_eGT_2025_7809_Cast_04.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:97c2514e-0c23-45fa-a283-9e9e8fb07177/original/as/1920x1920_eGT_2025_7809_Cast_04.jpg","9x16_A6_2026_9257_1_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:424c701a-1022-4951-9b10-19ac1ce76517/original/as/9x16_A6_2026_9257_1_01.jpg","1920x1080_VST.jpeg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:0d6cea04-7412-4955-98ec-0b9aaa34c237/original/as/1920x1080_VST.jpeg","16x9_Audi_WKR_2026_Keyvisual2_02.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:7ba429c1-3761-4f69-b612-e286dca4abfa/original/as/16x9_Audi_WKR_2026_Keyvisual2_02.jpg","16x9_as_2023_5877-32641384_01.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:e88cfb16-2ce0-4093-90de-e462cf6de548/original/as/16x9_as_2023_5877-32641384_01.jpg","1920x1080_A223159_large.jpg":"https://emea-dam.audi.com/adobe/assets/urn:aaid:aem:11aed372-f8ba-41a8-8582-fcdc7beb44b8/original/as/1920x1080_A223159_large.jpg"}</t>
+  </si>
+  <si>
+    <t>language-masters/de</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>2026-10-28T13:53:38.254Z</t>
+  </si>
+  <si>
+    <t>Modelle, Aktionen, Angebote | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/</t>
+  </si>
+  <si>
     <t>language-masters/de/elektromobilitaet.report.json</t>
   </si>
   <si>
@@ -79,6 +135,30 @@
     <t>2026-10-27T17:21:25.440Z</t>
   </si>
   <si>
+    <t>language-masters/de/neuwagen.report.json</t>
+  </si>
+  <si>
+    <t>["fragment","cards-carline"]</t>
+  </si>
+  <si>
+    <t>{"cards/audi-a2-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbdRSH_37Zdre57syy0006TZadSVhH0k4uZjeVgCkqVKFWe_PykE6S2c3UTTZMJjFVoVgURFsQqfUGWltB0K0ofbBSKaLimyIoKEXQ9klwRanQegFx4svHOYfzO_w4nLP2q9jQdwUP71z7Y_OfGyf2_YQQw64QgZ0i0O0s3ySEaLLJaVvL9nY_3zxr5bL20Mtag-72vJlfyFb3F3LDbM7cnbVWVrLVfEyM-xqxwVci-xiL-IiqPiaOif85mnlqhDdHOfmA3z30gwdHOhGd6rsrXcu12ttcu9dd7fScgS3N22WrbOVz5aJdr9cXF0v1smUu1QvlJdMsFXNmwS6Um43GrQ3ZH_GOCDTtvpg8XK_1nKZdyxVNc1gyc2Jjq9GxHFeMjZxjPMvWK0w_j7IX5SWU8xhPEf-XRJXESRJrJC5gHEB9ldQ5UhdJfY3xHHPX0cA4jnYY7TfSf5N5gUwdcTvGLsIu4deIvE1MIbbAzJNs-QK1g1ondRvpXaRvIOKIB5A-Rp5i-iRKkcQSqow6ix5AN9Avk_6A4DjBtwiXiBYxHkc6iryKfAbjPuKPEL-GHkN_A_1L0iVCdxO6jrSOcpbIe0QuIe1AqiF9hvQV8r3IfaZPEP8IdTfzt5C8TPIGyX9ITZCaJDWL8RBzv6Al0E6heWiX0Pej_05aJq2T_pHIaSLniXWY_JCbTxNbZKbHzCsYh4ifIXGQxEUS36A2SH5C8lNi3zP_NMozGMeYu0L6c8Q44ijGnWy6SvB-gm2CrxM8S_AHQocIHSF0lXCYsO__BJFviUaI3kP0INEu0ePEqhjvE3-RLV3Ud0ntIDVg7i-0eaS7kCPE_c0cwdiK9jPRdWLrSGNIL2M8gfIYynf-aSzbnYHjrnbadser7PX6TWc186jT9FqVolkuZVq2s9zyKgVzIZ-xVrotq-K5fTvTsNq2a1WqB_bk76hVa4WaaZoZq-N_hef4B1rJtG3PalqeNbDdnl-p5KcCfvN_25OpJF0DAAA.png","cards/audi-a3.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf37Sbm16c9N7S--SNCSSe28oldibP23aaXQd4sMQlc46RCH7tbltU5o_pjcxVQRfxL1MfHD-mYhSB0O3iaKIsLHNfwMZm4IPSl8se1FZVXDgJiJ668uHcw7ne87hcM7pX0VvuyV4fP_pG3tu7ep7ZAshuk0hAsdEoFlfuk0IUaG_WpNL7rjv77FlPuN2vYzsNMdzTq6YkfmmzDxQzczM5ae6mal1JyNXV8Nity8Uvb6cuI-efh_qAR99afE_dwpv7OCrHZ9swM_u-sZjOzqhDrVbq03ZkrU7W-5as1Ffq3ZcbXSqMF-UE9Pu4qKzODE1n5XTrnQL85N5N5vP5hcmnEJ-olJcmNf9El-KQMVti8GV-fJateKWswXH6U46WbFrar0j6wuiZ2d8kreIX2P4JYyDGB9gfETkBtG7iY0RmyH2MrH3iH3KyL_Ej5M8Q_IsyW9JbZL6A1NgrmD-jv0P6XHSDyL2ETyP0iJ0EvVewgaRZ4mcYeQS8QZxSfwoY1Wsq9g3EVFEDn-92jm0y-igDzH8NsZdxBaJ61hjWJvYHxLsJXgCpYhyD2oBzUNfRT-FYRCtEL1M9Ddi21hhrBRWAauM9RbWFez9DBxg4E-Uj9Hvx3gH4xKhrwl9grqBthetjPYF2lX0NPok-kPoHsNHiZ4lPsvoHSQ2Sdwk8TfJHpKDJG8ndR0zgvkKpod5DmsO6ydsHdvC_hHlEMoJQq8S-oVwnfAbDM4xuMXYBcxpIh6R40S-Yeww0Q1ifpcFEhdJfI55AUUj_ANDRYaXMY5gXCTyBJEVIs-TrJHawi5jP4n9OvZniN2IZ-jfJjhLsEbwOgOHGVhn4BqKgvIuyvuEXiT0Heoh1Abqc6gvEJ4h7LNL9E1GmsRPkThPci_JDqm_MEfR9hGdJbpOXMG8gvkz9hGUAMoI6jHUbcLbaH1or2E8jfG9f2hLbr1TbTXqNbfulQ567Uq1kX6qWvGWSwVnejK97FaXlr1S3inm0nK1uSxLXqvtphdkzW3J0syjD-fuK8-U82XHcdKy7j-aV_XPvZSuuZ6sSE923NaaHynlhgJ-8n8dZGj4sAMAAA.png","cards/audi-a5.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59Nmmazs5uZkMnudNyVndklpKyd_cmmqa4YlVx40YppKuLF9iQz7m6S3Syb2TSSXnhT9cYfsPhTlUJtb7QopVKsLf5bCmJBvbCooO2VYkRQaSoiOPHiPJz38L3fdw6858xvorfbETx675k_R25t33HgJ4RYawsROi5C7VZtmxDCpb_RlDVvd6BHbDme89b8nFxt7y44hYlcoKdmS85abs_herAWc3JpKSb6Ap_oDdzbTgXoGQwQfS3Ajrz4n1t9n9zClS2NEwqq14LNI1s-ER3qdpbasiObd3S8lfZya6Wx6qmj5cmSnHdLXn6uLKXn7ilPFCeLjisdKR23UJ4syrzjlvNlLWhxWYRcrysGF-aqKw3Xq-ZLjrNWdvJi-2PdgmzXRM_W7UmPc9t1hp9Hn0E_R_wWibswxjCmMI5hvInxHqkcqdOkLpL6ivQ10n9gCawFrN_JjpAtkl1E3ENYIXyU8AdEOsR04uvE32HnZcwW5hzmM4w1SN2J_QL2VTKbiALqJbQhho-hT6AHE2uYGuYodgh7DPs7MmcJ9xE-ReRuoiVUH62F9jn6LhKLJL4g8RfGBlY_dgw7jV3FPkEmz8ADDNwk8i5aHG0a_Q2Ut1EuoJxHuYm6F7WKKlE_Rb2KlkUbR9uP1iVxEXMf5hFGd5H8nuQmyX9I_kuqh9Qg6Sukf8UysF7E8rEuYc9ib5LRyNhk9pP5kchJlJdQzqH8QqxF7FUGZxm8gLGONUl8hfhxxg6ROInxMMZ5jPcx50l-RPITrA-JaMSuMXSD4Tr60-gfM_Ic8QXiR8lUybxC5rMgoog-xBH6NwjfR3iGcJPwDwwcYmCdgRtEIkSC9z6L8g1RhahJ9AliU8QOEHuK2An0aRKvY1xnZxvzLcyvSe0ldZDUKum_sUZRp9EUEg-ReBwzgvUl1s9EQkRuJ7pBbAO1F_Vl9HX0b4O41bzWaqOz3Gp6Lb8y43fdxnL2cMP165WSM1nO1r1Gre5Xis5EISuX2nVZ8TtdLzsvm15HVqYOPli4vzpVLVYdx8nKVvDb_EYQ-kq26fnSlb5c9TorwUmlMBQKiv8DYOrdkbUDAAA.png","cards/audi-a6.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAA_1vzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grz9Wu1QZ56rnMhy1ePSvpKdrvVd7gyMAK1MXYByRYGIEE3z8gwWHDACZB5oEN3QniMxkyMzCwVgAZkQwgwMdXWpRTkFiUmKtXnplSkiGoYUAkEGZ3cQ1x9PQJBgCLqOBV6QAAAA","cards/audi-a6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcBRDHN79rPrrZu81uyOb2ut5pdveMkbN730nlxCsSS5FWiaaID9dNbnN3MXc5LntnpBVUKPiiKIIWoURK6YMGixSK1KKtXxQFH-xLLT60FaFiRFBoFVHc-PJjZpj5DzPMbP4q9Hc7As_s3fxj_M-BoSevIwjrbUEInRBC7VatTxCEKjsbTbfm7Q788Sm3kPLW_ZTba-_OOJliqlzw_M5qq9xzW36q_FQ-vZ6azZdT7sqKLAwG1UJ_oNF3IMCOwQCRcwGGDgn_c1v9hW1c2vZxQkH2emA8vV0nREa7nZW223GbD3S8tfZqa63R85TJ6aWiU83PLC1OZ2fcpXRmKVtYKGa8fCGbzhRzmYVc2ssWpxc9NZD4UghVva4wsrxQWWtUvUo65zjrBSctDNTqeXfBFXZsz8A9j3HXDcZeR5tDexvtLLqI_i-xMrE3iG0S-wjjOIkUifdIfEziChNXmbiNCaaIuYz5G8kEyf0IDyOGEMOIx5A6SBvIGtEjRM-w6yuMFsYCxqtMNUg8iPUm9j7sOwgZlAuoo4ydQSuiBX1rGCrGJMY-rBDWFNY17A8RBxFPId2LVEB6iEgOdRX1AloI_Vn0b9B_x5KxbKw8VgVrA-tr7BzDexm-jbKFGkWdRTtN-APC5wmfI3ISRULZg1JBcVE-R_kW9SBqF_0ixgGMo0zeT_wa8TvE_yb-D4khEiNMXGbiF8wY5luYPuYnWPNYt7BVbB17P_ZB7OtIpwi_S_gs4Z-RW4y8jDlDdI3oO0wdRj9J7BCx8xhV4heJf0b8J8xPkRTkq0yFGKujvYJ2ifE-ostEj2FXsL9AGEQ4ys6biI8iziE2EX9g-DDDRxi-iSQhTSMFM75G-AqRMJEXkcvI88gvIW9w32W0WfQTxG6wq43xPsZ3JPaQ6DHxF-YkyiyqjP4E-vMYEuYtpAGku4lsIW-h9KMcRwlW9yPa98Gt1bxWrxF8QtNr-aU5v1ttrCafa1T9einnzBSSda9Rq_ulrFPMJN2Vdt0t-Z2ul1x0m17HLZXnH888UilXshXHcZJuK3g4vxFcfCnZ9Hy36vpuz-usBZFSZjQUJP8HmeY5vLgDAAA.png","cards/audi-q3.png":"https://mediaservice.audi.com/media/fast/v3_x2TW2gcdRSH__22adrN7mxmQqY7kzEjmd0xiayZvWQ3qSwYKRH6ULUxVVHYTrKzyYbsZt3Mxpj6oILYlxYfWqsVaUl9sValREOhRaXRIgoqIiit4OXJS0TESxUfdOLLxzmH8zsXOOf8z6Kt1RQ8dOf533b_tWPnfd8gxHJDiNCqCDXqM9uEEGV2VWvujDcU-LvtR7Ipb9lPuUuNoYyTKaTGJrPZfGo8m0658_Ope7MTkwdT---KifZAKdoC_bbrAUI_BZBCAXY2xf_cqry6hdNbPk4oyF4OjAe3dELqajXnG27Trd3W9BYbC_XF6pIn9-enC-VCrpAv5Nx0biSbH3GGR0eGc9NuJjc65Xjl0dzUcMXzRpSgxAciVPZaonNuqrRYLXuldM5xlvNOWuyozE25KzNi-9b8DJzjpgrdz6JOoJ5EXWPgJNpb6IPoY-jH0c-hX6TnX4xTmCnM1zAvYX5K3zX6_sASWBWsX7B17CHsfYg7CEcJv02kibSXmEr8SeJv0HMVo44xhXGUwSrm7SQ-IXkDoSEyiAeQLyN_iNKG0kX3cdQCegVDwegnESIxSOIayQuE2wm_TKSAlENeQamjrKOqaGW0j9B-JxEjsULiNIk1kmk69tHxJ5E3UcZRz6JeJfo60StE15FWkdPIe5BLyBeRN5A_RrFR8ih3o7ToPop2CWM_xmH6b6X3Or036P0HcztmJ-bN9P2KpWM9h-VjXcZ6n8QkAxdIKiQ1kl8TPUN0jegPxOrEXqRzks4NBs4QGyG-SPwUg4fQVtHvR19HD3qV6b2C9Q6xL1G-petHumdRj6C-y8AG8TniT2NWMJ8iWSL5Asn3EO2Ix9m1SfgA4Rrh04TPEv6KjkN0HKbjOyIRIq8QCbY-RvRzpCjSw0g-0hNIx4iNEXsG7SV6GhivYnyGuQdzib6_sfqRx1GiaAfQHsOIYH1P8giRENIJpE1im8htyM9zywnUL4Kjm_HqS9XmQr3m1f3ihN8qVxfsR6tlf7aYc0bz9qxXnZn1i1mnkLHd-casW_SbLc-edmte0y2OHbwns7c0VsqWHMex3XrwdX41OP2iXfN8t-z67pLXXAwixUxXKEj-D7iZcKa9AwAA.png","cards/audi-q4-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbZRiG_z5xu9scJjuzbHYnO2ZKJgnr2Ngkm002lYCpB2hBtK0tniBOkkk2ZZNNZydxoVrwSlEKVfCMrIjsha2HpSCFSlmseCMekAWlN9q9EMWKoNB6QHHizcP3_nzvx8fP-537RYz0HcEj-8_9PvXHzrEHvkeI1Z4QPkf4et3WDiFEg13tjtWy93p6KnUin7ZX3bQ16O3NZXLF9CFPu85yN105OpctpBdKVtpaWgqLUc8pRjz_jjc8-NY8SHs8jJXF_xxOfn6ItaEm6_O6V73ioaFPSBN9Z6lnOVbnNsde6S13V9oDW57N1edzuVKzUFtoWtZ8bq5YLxXtUq1uFbJ2MZ9tFoqFYqlWyCjeiAvC17D7Yvx4rbrSbtjVbD6TWS1ksmJnM9-yFjvipuH-7L4TbZvJM0SOEHmZyHlUGfVfohWizxJ9h-gFzGNor6G_i34R_SviV4hfxwBDwjiO8SvJv0i9QKqOuAfzAP4QQYfg64TWCUcIF5l-iun3mfkUrYtWQ7-dxJckD5C8gVAROcSDyB-hTDC5QSRPtImmoM2S8JEwSVwhuYF_FP_bSHnMe5G7KD2UdcxDqA3Uz1B_IxEmMU9ijcTnJAsE9hO4TmSd0CWkt5D3IVeRLeTLyF-g3IfiMnkadRPtMNqTaJeZvZXYNrEbxP4m9g_6GPo4-m70M5gPE_8ZI4rxEoaLcYnEUW7ZIKmQVEl-R-hNQucJ_US4y_iHRE8SXmB6wPSrqOtELxLdQmsQ2yT2McYmQYXwtyhXMfcQeYbIJlNb6KeIXyVZJfkJYhTxBObd7NrGfxj_CQI-Ao8ROElgm2AQ8yDB9widJrSFFEJ6FKmH9BzhCuYHhJ9GfZGZHtpZtK_R96H3iP-JMYt8B0oI1fu6U5g3Y_xIcAbpGuFryCPIryD_QOQbL0Qtuztoe-nu2F23fMTtN9rLqcfbDXexnM-UCqlFu91adMtzmWIuZS31Fq2y6_TtVN3q2I5Vrhy7P3dXtVKdq2YymZTV9a7IbXtRLqc6tms1LNca2M6K91LOTfi85v8AtYt2u40DAAA.png","cards/audi-q5.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSk_IztUhB2olJGHYTn3jH02vseip-3cZHh4ynHf3yc3_GdgBZrDOB1IMJ8FEvwMQIJjPYQE2VADIiaC-EyGzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggHJwayh4wAAAA","cards/audi-q6-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbZRzHn32ytV1ySXpXd81lZzJyd7FW4i5Z_qyTiJlSRcQpdRPxRXZpLmlqk2bJpXbUF74ZE2GgKDIEmXT6RosiA5Epbk6RoSDi3mjxxTpRJlYEhU0RxatvPjzfH7_v73l-8H3WfhU7Bj3BkwfX_hj_c2jksasIsdwVInBSBLqd5jYhRJ2drbbTdPf6ejztFDPuspdxlrp7c3aulDnma6-32MlUDuezy5lGoZ9xFhaiYth3ih2-f9uQj8CGj8hbPkZ-Ev9za_LxLTy_pbEDfveyf3hiyyciY4PeQtfpOe07e26_u9jpt5ZceaLounat6GYbDddxC7PZUqM-lSvUCo1sPZfN5gu1UqHg5PY3FH_EBRGouwMxOl-r9lt1t5rN2_Zy0c6KoWaj5mQdsX3r_ey5l1s32PUC6gzqObQQ2r_EK8RfJL5G_AP00yQzJN8k-SHJK6TWSd3AACOIMY_xG-kk6YcQ9xAMEAwTPIHUQzpDVCW2Quxddn-O3kGvoZ9iskXyLsyXML_GegDrJiKH_BHKGLteRi2h-lc30RX0CcwA5iTmOtZ7BIcJvoF0G1IR6W4ieZQ2ynnUANpTaF-i_Y4ZxUxhVjHPYH6BlSd0kNAN5E2UGMo06lnC7xC-RPh95APIVWQH-VPkr1AOoQzQLqI_jL7CxB0k1kncJPE3iX9IjpAcJXWZ1C8YcYxXMDyMjzEPY17HUrA0rAexDmFdRVol_Drhc4R_Jtph9BjGFLE-sVeZPIq2Svxx4ufR6yQukrhE4keMC0gK0W-5ZRb1OdRPGB8jNk_sBFYV6zPEMOIZdl4jeD_BGYJtgt8TOkpohdA1JAlpP5K_2inCV4iEiehEniVaIXqE6Eluv4w6jfYa8Q12d9HfRv-G5AFSf2FMIE-jhNEeRTuOLmFcRxpC2kNkk-gm8nbk08iryD-gfucnq-l2llp-5NtuxyvPeIN6azH9dKvuzZXz9lQxPee2mnNeeZ9dyqWdhe6cU_Z6Azc967TdnlOuHHkkd1-1Ut1XtW077XT8r-W1_HyX023Xc-qO5yy5vb5fKefGAn7zf7KBWguiAwAA.png","cards/audi-q7.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoTk_IztUhB2olJGH4Wdzv6Sh50eFh52zTiU5L5xc0nYhn4EVaA6jOJBgjgASfEeABEcnA5gE2ZABIvJBfCZjZgYG1gogI5IBBPj4SotyChKLEnP1UlKTStMFNQyIBMLsLq4hjp4-wQBRTCXI4wAAAA","cards/audi-q8.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcdRiGf3m2SdvNzG5m4k53N0MGd2a2IZJmdpPmn11pahERtNLWFvGwmWRnk02zk83ubJraKnoQvFQvxaJCe1AiaBWCImKLtBYaghiqHpSe1IuK6cWiNeSgk14evhfe7-U9fN-Vu6K1WRe8cOjKvT3_tu06_jNCLNWEiKyISM2fbhFClNhdqbrTXn-o9-gLI33eUtDnLtb6805-uG9hpOb2DVbLfe7cXFzsDP2iNdxqORAicj1E7EaIXSviAR_kbePctiYXCd1L4fD89p6IdTbrczW37lb31b1Gbd5vVBY9pWfUy40MDU9NjXiT3vDkaHl_bsDxyrncaFggP-KW97vuwECp7KhhxJqIlLym6JidLDYqJa-YG3ScpSEnJ9oGq4EzmRc7tlvz8Brd_WjH0D4lZZM6QLqX9DjpC6Q_JP0FRj_GMsZVjHWM78jcJvM35gTmX2RlsofJ-oiDSHXkZeIaiSbJl-m6he6jT6Cfp7dC5g-sd7DWse8j9hF9FOVNlGuonSQuoA2TnkXvRN-L_iRWBKsX6w52Avsk9grRVqLvI-1FGkJ6DDkgNojyNMqLqPOoqyS2SL5Hyif1Dan7pDcw2zA3seJYJlYR6zLW19iP0_4U7f8gfYb6BNoy8m3kz5HvIm-hjKEUUVyUmyjrqD2oBdQjqM-hNkmcJ7WK_gz6l_Q8QvcdurcwdmB0YNhk_sR8CzPAvIZ5A_MW1gms_7BV7BT2EewNpA-QLyL_Rtwn_i4dx-m4h5nHHCXZJH0VSSH-Ew9tkphBex3tOskxkrMkX8M4hV3GXsB-G3sN0YLYiTjH7g2ih4geJVolukr7JO1naf8VSUb6COkT5AnkN5B_ICYT04m9Qnyc-KvEL9PRQ-oS6V_oqqF_jP493V9hjGGcxFgks4nZg3KQ1FFSZ9AlzG8xf0dqQ-oitkF8A6UV5SLaWbRLaDfRfgzv7iXPX6zU5_2q5weFY0GzVJnPnq6UgpnCoDM6lJ3xKtMzQWHAGc5n3bnajFsI6k0vO-VWvbpbGD_xbP5wcbw4UHQcJ-v64bsFlfD6C9nG1HwtdJw-5Z1peAtNz5_yCvls1Qvckhu4i169EfoK-c5IGPE_puUsMswDAAA.png","cards/audi-q9.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSU_IztUhB2olJGH4dPkY46s-6KbtFgT_-lEnzY4KnLkFAMryJzrQILZFUjw6wAJjnYGMAmSiQYRxSA-kxEzAwNrBZARyQACfHylRTkFiUWJuXopqUml6YIaBkQCYXYX1xBHT59gAGx0n1DjAAAA","cards/audi-e-tron-gt.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGH4XjRqu9uj7VdK8UFWr2dj9dMP95Rw8AKNIpxPpBg0QISfL-ABIcHA5gEWZIJIk6C-EwWzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggEPp39D5gAAAA","cards/audi-nuvolari.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjDEBjWe-dDzqpFyy9ofdnj-Hin56m76xmYGRjYGxgYWCwYQIBPuLQopyCxKDFXryi1uCA_rzizLFVQw4BIIMzu4hri6OkTDAD_J8cizwAAAA","cards/audi-f1.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjD0CK89NsGXslvP2aeuao66f8-K6u9DgzMDAzsDQwMLBYMIMAnXFqUU5BYlJirV5RaXJCfV5xZliqoYUAkEGZ3cQ1x9PQJBgBHdTswzwAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen</t>
+  </si>
+  <si>
+    <t>neuwagen-finder</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:40:09.576Z</t>
+  </si>
+  <si>
+    <t>Modelle | Audi Deutschland</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/</t>
+  </si>
+  <si>
     <t>de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
   </si>
   <si>
@@ -247,6 +327,243 @@
     <t>https://www.audi.de/de/neuwagen/q5/q5-suv/</t>
   </si>
   <si>
+    <t>language-masters/de/neuwagen/a2-e-tron.report.json</t>
+  </si>
+  <si>
+    <t>["fragment","cards-model"]</t>
+  </si>
+  <si>
+    <t>{"cards/a2-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbdRSH_37Zdre57syy0006TZadSVhH0k4uZjeVgCkqVKFWe_PykE6S2c3UTTZMJjFVoVgURFsQqfUGWltB0K0ofbBSKaLimyIoKEXQ9klwRanQegFx4svHOYfzO_w4nLP2q9jQdwUP71z7Y_OfGyf2_YQQw64QgZ0i0O0s3ySEaLLJaVvL9nY_3zxr5bL20Mtag-72vJlfyFb3F3LDbM7cnbVWVrLVfEyM-xqxwVci-xiL-IiqPiaOif85mnlqhDdHOfmA3z30gwdHOhGd6rsrXcu12ttcu9dd7fScgS3N22WrbOVz5aJdr9cXF0v1smUu1QvlJdMsFXNmwS6Um43GrQ3ZH_GOCDTtvpg8XK_1nKZdyxVNc1gyc2Jjq9GxHFeMjZxjPMvWK0w_j7IX5SWU8xhPEf-XRJXESRJrJC5gHEB9ldQ5UhdJfY3xHHPX0cA4jnYY7TfSf5N5gUwdcTvGLsIu4deIvE1MIbbAzJNs-QK1g1ondRvpXaRvIOKIB5A-Rp5i-iRKkcQSqow6ix5AN9Avk_6A4DjBtwiXiBYxHkc6iryKfAbjPuKPEL-GHkN_A_1L0iVCdxO6jrSOcpbIe0QuIe1AqiF9hvQV8r3IfaZPEP8IdTfzt5C8TPIGyX9ITZCaJDWL8RBzv6Al0E6heWiX0Pej_05aJq2T_pHIaSLniXWY_JCbTxNbZKbHzCsYh4ifIXGQxEUS36A2SH5C8lNi3zP_NMozGMeYu0L6c8Q44ijGnWy6SvB-gm2CrxM8S_AHQocIHSF0lXCYsO__BJFviUaI3kP0INEu0ePEqhjvE3-RLV3Ud0ntIDVg7i-0eaS7kCPE_c0cwdiK9jPRdWLrSGNIL2M8gfIYynf-aSzbnYHjrnbadser7PX6TWc186jT9FqVolkuZVq2s9zyKgVzIZ-xVrotq-K5fTvTsNq2a1WqB_bk76hVa4WaaZoZq-N_hef4B1rJtG3PalqeNbDdnl-p5KcCfvN_25OpJF0DAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2-e-tron</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:40:13.643Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a2etron</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2etron.report.json</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a2etron</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:15:54.156Z</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/a3-limousine.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf37Sbm16c9N7S--SNCSSe28oldibP23aaXQd4sMQlc46RCH7tbltU5o_pjcxVQRfxL1MfHD-mYhSB0O3iaKIsLHNfwMZm4IPSl8se1FZVXDgJiJ668uHcw7ne87hcM7pX0VvuyV4fP_pG3tu7ep7ZAshuk0hAsdEoFlfuk0IUaG_WpNL7rjv77FlPuN2vYzsNMdzTq6YkfmmzDxQzczM5ae6mal1JyNXV8Nity8Uvb6cuI-efh_qAR99afE_dwpv7OCrHZ9swM_u-sZjOzqhDrVbq03ZkrU7W-5as1Ffq3ZcbXSqMF-UE9Pu4qKzODE1n5XTrnQL85N5N5vP5hcmnEJ-olJcmNf9El-KQMVti8GV-fJateKWswXH6U46WbFrar0j6wuiZ2d8kreIX2P4JYyDGB9gfETkBtG7iY0RmyH2MrH3iH3KyL_Ej5M8Q_IsyW9JbZL6A1NgrmD-jv0P6XHSDyL2ETyP0iJ0EvVewgaRZ4mcYeQS8QZxSfwoY1Wsq9g3EVFEDn-92jm0y-igDzH8NsZdxBaJ61hjWJvYHxLsJXgCpYhyD2oBzUNfRT-FYRCtEL1M9Ddi21hhrBRWAauM9RbWFez9DBxg4E-Uj9Hvx3gH4xKhrwl9grqBthetjPYF2lX0NPok-kPoHsNHiZ4lPsvoHSQ2Sdwk8TfJHpKDJG8ndR0zgvkKpod5DmsO6ydsHdvC_hHlEMoJQq8S-oVwnfAbDM4xuMXYBcxpIh6R40S-Yeww0Q1ifpcFEhdJfI55AUUj_ANDRYaXMY5gXCTyBJEVIs-TrJHawi5jP4n9OvZniN2IZ-jfJjhLsEbwOgOHGVhn4BqKgvIuyvuEXiT0Heoh1Abqc6gvEJ4h7LNL9E1GmsRPkThPci_JDqm_MEfR9hGdJbpOXMG8gvkz9hGUAMoI6jHUbcLbaH1or2E8jfG9f2hLbr1TbTXqNbfulQ567Uq1kX6qWvGWSwVnejK97FaXlr1S3inm0nK1uSxLXqvtphdkzW3J0syjD-fuK8-U82XHcdKy7j-aV_XPvZSuuZ6sSE923NaaHynlhgJ-8n8dZGj4sAMAAA.png","cards/a3-sportback.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluojE_IztUhB2olJGHQeZ41JXLxUv_fz3__P6DfNdZjr9NPBhYgeYwyQAJFk4gwecFJDjUGMAkyIZFIOIoiM9kyMzAwFoBZEQygAAfX2lRTkFiUWKuXkpqUmm6oIYBkUCY3cU1xNHTJxgAGxNEj-MAAAA","cards/a3-sportback-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf36ybm1yc9N7S9MkDYnk3puVSuxt_rTNNLKM4UNf1NU6RCH7pblt0zVpTG9r-jRfxD048UGtTkSpA1E32RCGMN3mvyHK9qCC0hfHniqr-FBxisi89eXDOYdzvocD33P2N9G10hY8dejszsBfe7sfv4kQnZYQvnXhazXn7hFC1OipN-ScM-LlA_tlLuN03IxcbY1k7ex4RuZaMlNenqpmytO5iU5mYm02IxcXQ2KfNyq6PAHiHvb0eFAnPXSnxf_cld7Yxde7OaM-r7vjBU_uzgm1b6W92JJt2bi_7Sy3lprL9VVHG8raM_aMLNhFe2KskB8fy-Wrs8VcbrRaKxbz1UKhWpgYLcqs1D2Jr4Sv5qyI3oVqZblecyqjedvujNmjYu_E2pp0OmLP7gGkBojfov9lwlOEzxP-mMgO0QeJDRMrE3uF2AfEPmHwLvHTJM-RvETyB1KbpP7AEBgLGL9j_Ut6hPQk4iD-yyhtgu-hHiYUJtIhco7Ba8SXiEvipxiuY97AuoOIIrKIBbRP0b5Fu4veR_87hB8gNktcxxzG3MS6gL8L_xmUcZSHUPNoJ9CPo79I_xbRGtHviO4Q28YMYVqYBUyJ-TbmdaxDBCYJ_IlyEf1hwu8SvkbwG4IXUTfQDqBV0L5Eu4GeRh9DfwTdpf8U0UvEjzB0H4lNEndI_EOym2QvyXtJ3caIYLyG4WJ8hjmNFcDSsUysX1COopwhuE7wV0JNQm_SO03vFsNXMIpEXCKniXzP8DGiG8S8LTMkrpL4AuMKik7oZ_qW6J8nfJLwVSJPE1kg8jzJBqmbWBWsZ7DewPocsQ9xgp5t_EfwN_DfJnCMwBqBWygKyvsoHxF8ieCPqEdRj6M-h_oCoTIhjx2ibzHYIv4hicskD5BcJfU3xhDaQaKPEV0jrmBcx9jCOoniQxlEXUfdJrSN1o32OvtfJfyTZ7Q5p7laby81G07TLU25K7X6UvrZes2dL-Xt4lh63qnPzbulnD2eTcvF1rwsue0VJz0jG05blspPPJo9XClXchXbttOy6b2aW_fsXko3HFfWpCtXnfayVyll-3xe83-BTFXvsgMAAA.png","cards/a3-allstreet.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf37Sbm16c9N7a2-TNCSj948lEnubpGk7jS5DfOiL0lpFfUhvmtsms0ljetulguiLOISJD-p0IkodiHMbiiLCxjad7sExGfqg9MWxF5VVRQdOEdEbXz6cc_ie7-HAOSd-Ft3rLcFj-0_cGPpzV8-DVxGi3RQicEQEmo3lW4QQFXprdWfZHfPzoducbNpte2lnozmWsTOTaSfbdNLFtblyujifnWqnpzaX0s7KSljs9ltFt29A3EdXrw95xkePJf5nx3qrgy86OeMBX932g0c6fUIeWG-tNJ2WU7-j5a41VxtrtQ1XGV1cmnDLuelcpmy7uYlyPpOfXHTzU-XJnJ2z85klt1zJ58YzedW3-FwEKu666D9QLq3VKm5pPGfb7bw9LnZNbR60NxdFV2cB9hwnfo3BF9Hm0N5H-5DIDaJ3EUsRKxJ7idhxYp8w_C_xoyRPkjxN8goj24z8ji7QF9B_xfwHawxrBrGP4FmkFqF3kO8hrBF5ishJhi8SXyXuED9MqoZxBfMmYgiRQTRQzqBcQgV1gMG30O4ktkRcxUhhbGN-QLCb4DGkSaS7kXMoHurjqKfQNKIVopeI_kJsByOMoWNMYDgYb2JcxtxP3wx9fyB9hHof2ttoFwl9Sehj5C2UvSgllAsoX6FaqHnU-1E9Bg8TPU18ltHbSWyTuEnib5JdJPtJ7mHkOnoE_RV0D_0MxjzGD5gqpoH5PdLDSMcIHSH0E-EG4dfpn6f_Aqlz6NNEPCJHiXxNaoHoFjF_yiKJ8yQ-Qz-HpBL-jlt_Y7CKdgjtPEO--ACRZ0nWGbmKWcJ8AvM1zE8RuxFP07tDcJZgneB1-hbo26TvGpKE9C7SKUIvEPoG-VHkFvIzyM8TLhJ-jnCb6BsMN4m_R-Isyb0kNxj5C30UZR_RWaKbxCX0y-g_Yh5CCiANI7-MvEN4B6UH5VW0J9G-9Q9t2W1s1Fqrjbrb8Apz3nqltmodrFW8aiFnT-etqltbrnqFrD2ZsZyVZtUpeK1111p06m7LKRQfeiBzb6lYypZs27achv9qXs0_94JVdz2n4njOhtta8yuFzEDAF_8HKx0DKrIDAAA.png","cards/a3-allstreet-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf36ydm1yc9N7a9MkDYnk3puVSuxtkjbZNLKM4UNfpqtVpg_pTXPTpDRpTG-79Gm-iEOY-KBWJ6LUgaibU4QhTLf5bw-Tqaig9MWxp8oqPlScIjJvfPlwzuGc7-HA95z9TfSstgVPHjq7O_xXb9-jNxCi0xLCsyE8rebCXUKICv31hrVgj7v58D4rk7I7Tspaa42nzXQuZWVaVqq4MlNOFWcz-U4qv15NWUtLAbHXHRU9rgBRF3v6XcjTLvqS4n92pTe7-KqbM-FxuztucKw7J-TB1fZSy2pbjfva9kprublSX7OV0Uwul7WzE5lJK1-u5HPl-Wp6ftLKZczqfNY2p8qVbLVs5tMTqivxpfBU7FUxsFgurdQrdmkia5qdKXNC9ObXj5t2R-zpHkBimOhNhl4gOEPwA4IfEdol_ACRMSJFIi8SeZfIx4zcIXqa-DniF4n_QGKLxB9oAm0O7XeMf0mOk5xGHMR7CamN_23kwwSChDqEzjFylegyUYvoKcbq6N9h3EYMI9KIJsonKNdQ7qAOMvQmwfuJVImq6GPoWxgf4u3BewYph_QgchblBOox1PMMbROuEP6a8C6RHfQAuoY-iW6hv4F-HeMQvml8fyJdQH2I4FsEr-K_hv8C8ibKAZQSyhco36AmUadQj6A6DJ0ifJHoUUbvJbZF7Daxf4j3ER8gfg-JW2ghtJfRHLRP0WcxfBgqho7xC9LjSGfwb-D_lUCTwGsMzDKwzdhltP2EHEKnCX3P2BzhTSLulnliV4h9jnYZSSHwM3d_y1CN4EmCVxjuJbRI6BniDRI3MEoYT2G8ivEZYi_iBP07eI_ibeC9hW8O3zq-m0gS0jtI7-N_Hv-PyE8gLyI_jfwcgSKBZwl0CL_OSIvoe8QuET9AfI3E32ijKAcJP0J4naiEdh1tG-MkkgdpBHkDeYfADkofyivse4ngT67RFuzmWr293GzYTacw46xW6svJ4_WKUytkzf1TyZpdX6g5hYyZSyetpVbNKjjtVTs5bzXstlUoPvZw-nCpWMqUTNNMWk331Zy6a_dCsmE7VsVyrDW7veJWCulBj9v8H5ueLKSyAwAA.png","cards/s3-limousine-tfsi.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf_uk3dr05qb31t4laUwk948lEnfzp__GomsZPoigdNYhPmQ3yTXNaNKY3MQU_yCIUB8mPlixii-z4KZTB4oIG9vwz8DJpg-CMhCG7EGxIjjYFB_01pcP5xzO95zz8D2nfxeD3bbgiYXTN_f-tXvo0esI0W8JEdgQgVaztksIUWW43nBq7j4_32s6-Yzb9zJOr7UvZ-dmMk6-5WQeqmfml_Kz_czsmp1xVlbCYo8vFIO-nLiPgWEf8oM-hizxP3cGn9jBVzs52YDf3feDx3d0Qh7rtldaTttp3Nt2O63VZqfec5XJqj3lOvnC9FzOrpSr2ZmCPTc15weV7Gy-Ui7n7enqrFuuTKn-iC9FoOp2xeixcqlTr7qlbMG2-9N2VuyeXet1ptbEwM753PUcdx5k_FW0w2hn0D4mcpPoAWJpYvPEXiP2HrHPmPiX-CbJD0ieJfkdqWuk_kTfhX4E_Q-sCaxDWH3EAsHzSG1C7yLfT1gj0ifyEROXiK8Sd4gfJ13HuIp5G6EjphAOyjmUy6iDqGOMn0TLE3uSuIqRxriGeYbgIMEtpBmk-5ALKB5qE3UTLUq0SvQboreIbWOEMSyMAoaDsYVxGTPLyAIjt5A-QX0A7R20S4S-JvQp8gmU_SgllC9QrqJaqAdQH0b1GD9O9CzxRSbvIfETidsk_iE5QHKUpE7qN_QI-uvoHvo5jCVMMFVMA_MG0hGkLUKbhH4l3CT8FqNLjD5L-gL6HBGPyJtEviV9lOgpYv6WComLJD5Hv4CkEv6RO15kfBltHe0ikRyRY0ReItkgdR2zhPkU5ibmFcQexDMMbxNcJNggeIORo4ysMfIzkoR0CulDQq8Q-h65htxHfgH5ZcLzhNcJ94m-zUSL-PskzpPcT7JH6m_0SZSDRBeJPk9cQr-C_gvmOlIAKY68gbxNeBtlCOUN7t5A-8E3Ws1t9urt1WbDbXrFw163Wl-1nq5XveWib89pa9mt15a9Yt6eyVnOSmvZKXrtrmtVnIbbdorzjz2SO1SaL-VLtm1bTtN_NK_u271oNVzPqTqe03PbHb9SzI0F_Ob_AJDFrGqwAwAA.png","cards/s3-sportback-tfsi.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf_uk3dr05qb31t4laUyk989KJS5N0qQdiy5l-LAXpbUO8SH7rfe2zWjSmNzWFPwHItSHiQ9OreLLLLjpnANFhI1t-GfIZENEUAbCkD0oVgQHm-KD3vry4ZzDOd_Dge8587voXmkJnpw6c3v3Xzt7HruJEJ2mEKE3RKjZWNghhHDprdXlgrc3yHfvkfmM1_EzcrW5N5fNlTIy35SZSnvmaKYym5_oZCbW5jNyaSkqdgWjojsQIBmgqzeAeihAjyP-57b0yW18tZ0zFgq6O0HwxPacUAdWWktN2ZL1B1peu7ncaNdWPW3EzXn5ucn5Uq6YnZOlwoQ74RXcsXxh3i0WCrmSLBZLBc8dn9QDiS9FyPVWRP-xo9V2zfWqY4VstlPMjomdE2tr7fE10bV9APc9y70HGHwVYwbjHMbHxG4T309ilESFxGsk3ifxGUP_ktwg_SHp86S_ZfgGw39i7sA8jPkHzhDOQZwOYorwRZQWkfdQHyJqEOsQ-4ihKySXSUqSxxmtYV3HvoswEeMIiXYB7Sp6N_oAg6cw8iTmSepYo1g3sM8R7ia8iVJCeRC1gOajN9A3MOLEXeLfEL9DYgsrimVijWNJrE2sq9hj9E3RdwflE_SHMd7FuELkayKfop5E24dWRfsC7Tq6g74f_RF0n8HjxM-TnGbkflI_kbpL6h_SXaT7SZsM_4YZw3wd08e8gDWLDbaObWHfQjmMsklkg8ivRBtE36Z_lv5nGL2EOUnMJ_YWse8YPUL8NIlgyxypy6Q-x7yEohP9kXteZHARYx3jMrEcsWPEXiJdZ_gmdhX7KewN7GuIXYjn6d0iPE24TvgWfUfoW6PvZxQF5TTKWSKvEPkedQG1g_oC6stEK0TXiXaIv8NQk-QHpC6S3kd6leG_MUfQDhCfJv4cSQXzGuYv2OsoIZQk6gnULaJbaD1ob7LnBMYPgdEWvMZqrbXcqHsNvzzjr7i1ZefpmusvlgvZyaKz6NUWFv1yPlvKOXKpuSjLfmvFc-Zk3WvJcuXxR3MHq5VqvprNZh3ZCF7NrwV2Lzt1z5eu9OWq12oHlXJuIBQ0_wckp76YsgMAAA.png","cards/rs-3-limousine.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbdRjHf_2k3dbmculd6TVJj8Tl7tJYibv8WdOOhdkhgiIonXWIL-KtubYZTRqvlyxFEN8M6ouJL_yzTQSZRTfdZKKIsDGH04EbTl8IyvDF9JVjFcHBpqjo1Tcfnufheb7P88DznP5V9LU9wdN7T98e-WPLtiduIES3JUTouAi1mgs9Qoga_fWGs-DuCPyRcaeYc7t-zum0dhTsQjnnFFtObmal-Gi9sZybni1OdnOTq52cs7QUFVuDatEXaKAH6O0PID8SYFtG_M9N9ROb-HLTJx8KsruB8dRmnZCH2t5Sy_Gcxv2eu9Jabq7UO66S3ek6cxNuyZkolwqu6-507ZLtlGpOfqI0X54su_nJwlRhyi2ogcQXIlRz22Lw4IHqSr3mVvMl2-5O2HmxJZjRO7Qqejd34J40SZ3hl9H2oZ1F-4jYbeK7SYyTmCbxCon3SHzK6L_ox0idIXWO1Lekr5P-HaMHYz_Gb1h_kymSmUc8zMAFJI_Iu8h7iGrEusQ-ZPQyehP9APoRxuuY17DuIrKIEsJDOY9yBeUf1CGGT6IVSMyjq5jjmNexzjLQx8A6UhlpD3IJpY3aRL2EliBeI36V-B0SG5iDmNsxS5gO5jrmFaw84b2E7yB9jPoQ2ttol4l8ReQT5BMou1CqKJdQrqFmUXejPobqM3yE-Dn0GbL3kfyR5F2Sf5HqJTVIyiB9CyOG8RqGj3EecxbzJpaKNYb1E9J-pHUiR4ncJNok-gaDswze4t63MKaI-cSOE_uG8cPET5IIutRIXiT5OcZnSCrRHxhqMbyItoZ2kZF3iB0kdphUg_QNrCrWs1jHsL5GbEU8R_8GAzMMNAiPEX6G8Crhn5EkpFNIHxB5ich3yHPIHeQXkF8kOk10jWiX-JuMttDfJ3mB1C5SHdJ_YmRRHiA-Q_x5dAnjKsYvWGtIISQd-XXkDaIbKD0oRxl7Fe374NAW3Gan7i03G27Tr-zz27X6cuZQveYvVkr21ERm0a0vLPqVol0uZJyl1qJT8b22m5lzGq7nVKaffLzwYHW6Wqzatp1xmsG3-fXg3CuZhus7Ncd3Oq63EkQqhaFQkPwfoqWeMrUDAAA.png","cards/rs-3-sportback.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf_2k3dbm5qb3lt4m6SWR3Nw0VuJukv5JxsJsEUFflNY6xId4m9y2GU0ab2-y9EV9GdSHiQ_-6RRBZtGpUyaKCBtzOB2y4RARlOHD9MmxiuBgU1T01pcP5xzO-Z5z4JzTv4q-tit4Yvb0rZE_9ux79DpCdFtCBLZEoNVc7hFC1OivN-xlZ7_vj2TsQtbpelm709qft_LTWbvQsrNz64X52ezMQqHYzRY3NrL26mpY7PVrRZ-vgO6jt9-H_JCPfWnxP3e1T-7iy12fXMDP7vrG47t1Qh5qu6st27Ub97rOemutuV7vOEqmUJuqFi17acIu1WpVuzhpT1vFxWo1V5p0nMJ0bnFqcbJULC6pvsQXIlBz2mLwyGJlvV5zKrkJy-pOWTmxx5_RPbohenc34K4kcZ3hF9Dm0c6gfUTkFtGDxMaJzRB7kdi7xD5l9F_0EyTeJ3GWxDckr5H8HaMH4zDGb5h_ky6QXkI8yMB5JJfQ28iHCGtEukQ-ZPQSehN9Ef0443VSVzHvIDKICYSLcg7lMso_qEMMn0LLE1tCV0mNk7qGeYaBPga2kaaRDiFPoLRRm6gX0WJEa0SvEL1NbIfUICmD1CQpm9Q2qcuYOYKzBG8jfYz6ANqbaJcIfUXoE-STKAdQKigXUa6iZlAPoj6M6jF8nOhZ9Dky9xD_kfgd4n-R6CUxSMIgeRMjgvEyhodxjtQCqRuYKuYY5k9Ih5G2CW0RukG4Sfg1BhcYvMndb2CUiHhEXiXyLePHiJ4i5nepEb9A_HOMz5BUwj8w1GZ4BW0T7QIjbxE5QuQYiQbJ65gVzKcwT2B-jdiLeIb-HQbmGGgQHCP4JMENgj8jSUjvIH1A6HlC3yFXkTvIzyI_R3iG8CbhLtHXGW2hv0f8PIkDJDok_8TIoNxHdI7o0-gSxhWMXzA3kQJIOvIryDuEd1B6ULYYewnte__Qlp1mp-6uNRtO0yvPe-1afS19tF7zVsoTVmkqveLUl1e8csGazqft1daKXfbctpOu2g3Htcszjz2Sv78yUylULMtK203_17y6f-7ldMPx7Jrt2R3HXfcj5fxQwE_-DzNW8rKzAwAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a3</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:15:58.463Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a3</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a5.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/a5-limousine.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59Nmmazs5uZkMnudNyVndklpKyd_cmmqa4YlVx40YppKuLF9iQz7m6S3Syb2TSSXnhT9cYfsPhTlUJtb7QopVKsLf5bCmJBvbCooO2VYkRQaSoiOPHiPJz38L3fdw6858xvorfbETx675k_R25t33HgJ4RYawsROi5C7VZtmxDCpb_RlDVvd6BHbDme89b8nFxt7y44hYlcoKdmS85abs_herAWc3JpKSb6Ap_oDdzbTgXoGQwQfS3Ajrz4n1t9n9zClS2NEwqq14LNI1s-ER3qdpbasiObd3S8lfZya6Wx6qmj5cmSnHdLXn6uLKXn7ilPFCeLjisdKR23UJ4syrzjlvNlLWhxWYRcrysGF-aqKw3Xq-ZLjrNWdvJi-2PdgmzXRM_W7UmPc9t1hp9Hn0E_R_wWibswxjCmMI5hvInxHqkcqdOkLpL6ivQ10n9gCawFrN_JjpAtkl1E3ENYIXyU8AdEOsR04uvE32HnZcwW5hzmM4w1SN2J_QL2VTKbiALqJbQhho-hT6AHE2uYGuYodgh7DPs7MmcJ9xE-ReRuoiVUH62F9jn6LhKLJL4g8RfGBlY_dgw7jV3FPkEmz8ADDNwk8i5aHG0a_Q2Ut1EuoJxHuYm6F7WKKlE_Rb2KlkUbR9uP1iVxEXMf5hFGd5H8nuQmyX9I_kuqh9Qg6Sukf8UysF7E8rEuYc9ib5LRyNhk9pP5kchJlJdQzqH8QqxF7FUGZxm8gLGONUl8hfhxxg6ROInxMMZ5jPcx50l-RPITrA-JaMSuMXSD4Tr60-gfM_Ic8QXiR8lUybxC5rMgoog-xBH6NwjfR3iGcJPwDwwcYmCdgRtEIkSC9z6L8g1RhahJ9AliU8QOEHuK2An0aRKvY1xnZxvzLcyvSe0ldZDUKum_sUZRp9EUEg-ReBwzgvUl1s9EQkRuJ7pBbAO1F_Vl9HX0b4O41bzWaqOz3Gp6Lb8y43fdxnL2cMP165WSM1nO1r1Gre5Xis5EISuX2nVZ8TtdLzsvm15HVqYOPli4vzpVLVYdx8nKVvDb_EYQ-kq26fnSlb5c9TorwUmlMBQKiv8DYOrdkbUDAAA.png","cards/a5-limousine-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2wUVRzHXz9LW9jO7OxM0-nuMO6anZlNU7My3W23FF1jlfTgATSlGONhGTqz3S3d7Wb_lJJy8IJ68U8i8Q9qSBAuSjSEhIAYDGqQxMhBDhI1UTxprPGgoRCjcerhffK-L7_v7_de8n1nfxe93Zbg2cfO_jl8t2_rvp8QYrUpROSEiDQbCz1CCJ9ttbq3EOwI9bDtTeSC1U7OW2nuyLv5yVyop-fG3dXczsPVcB3KeUtLiugPfaI3dPecDrElHiL2ToitY-J_bvZ9fhPXNzVuJKxeDTfPbPpEbLDbWmp6La_-YCtoN5cb7dpKoI5M-IV5t1Kc9wsFN7_TmypUKkXfrfgTk14hcItTYxWvGBT9iha2uCYiftAV8cWD5XbND8pj4667WnTHRF-lm_fGjogtm7cnM8x9txl6FX0W_TyJuyQfxhjFmMY4jvE-xkXSOdJnSF8mfZPMLTJ_YfVgLWL9gfMv2d1k24hHicpEjxG9gtRC0UmskfiI7dcwG5gHMV9itEb6IezXsG_gbCDyqJ-gDTJ0HH0SPZy4gKlhjmBHsEexv8M5R7Sf6GmkR4iNo66hldG-RE-RPETyK5J3MNax-rEV7Ax2GfskToGBJxi4g3QJLYE2g_4e8ofIl5AvIN9D3YVaRvVQP0e9gZZFm0Dbi9YleRlzD-ZRRh4g9T2pDVJ_k_qHdC_pOJnrZH7DMrBex-pgXcGew97A0XBsnL04PyKdQn4D-TzyrygNlLeJzxGvYaxhTZFokzjB6AGSpzCexriA8THmPKmrpD7D-hRJQ7nF4EWGqugvol9l-BUSiySO4ZRx3sL5Iowooh9xlG3rRB8nOku0TvQHBg4wsMbAz0gSUvjel5FvEpOJmcSeQ5lG2YfyAspJ9BmS72LcZnsT8wPMb0jvIr2f9AqZe1gjqDNoMsmnSB7BlLC-xvoFqQ_pfmLrKOuovahvoq-hfxvGbSForNRay4160OiUZjtdv7acPVzzO9XSuDtVzFaD2kK1Uyq4k_mst9SseqVOqxtk57160PJK0_ufzO8uT5cLZdd1s14j_G2dWhj6UrYedDzf63grQasdnpTyg5Gw-D_DpWoqtQMAAA.png","cards/a5-avant.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59NmmYzs5OZkMnudNwtmdklpKyd_U3TumJUeuGFFdNUxIvt7O5kd5PsZtnMppH0wpuqN_6AxZ-qFGq90aJIpWhb_LcUREW9sKig7ZViRFBpKiI48eI8nPfwvd93Drzn7G-iv9cVPHTn2T_Hbm7fcegnhFjrCBE6KUKddn2bEKLGYLPl1r09gR6z3ULaW_PT7mpnT9bJTqUDPTOXd9bSe482grWYdpeWFDEQ-ER_4N52JkDfcIDISwF2ZMT_3Or76BaubGmcUFC9Fmwe3PKJyEivu9Rxu27r1q630llurzRXPXWi4lay1fnKfK5WnHcK1b3T05mpQqWQyxdzxUxh3s1Vval8rljVghaXRajm9cTwQqW80qx55UzecdaKTkZsn-8V3E5d9G3dnl37ueUao0-jz6KfI3qT2G0YkxgzGCcwXsN4h0SaxKskLpL4ivGrjP-BJbAWsH4nNUYqR2oRcQdhmfBxwu8hdVF0outE32TnZcw2ZgXzCSabJPZjP4P9JclNRBb1EtoIoyfQp9CDiXVMDXMCO4Q9if0dybcIDxA-g3Q7kTyqj7aM9in6bmKLxD4j9hfGBtYgtoJtYZexT5HMMHQPQzeQ3kaLoh1AfwX5DeQLyOeRb6DuQy2juqgfo36BlkIroB1E6xG7iHkv5jEmdhP_nvgm8X-I_0uij8Qw41cY_xXLwHoWy8e6hD2HvUlSI2mTPEjyR6TTyM8hn0P-BaWN8iLDcwy_i7GONU10hehJJo8QO43xAMZ5jAuYVeIfEP8I630kDeUqI9cZbaA_jv4hY08RXSB6nGSZ5AskPwkiihhAHGNwg_BdhGcJtwj_wNARhtYZuo4kIQXvfRL5GyIyEZPIIygzKIdQHkM5hX6A2MsY19jZwXwd82sS-0gcJrHK-N9YE6gH0GRi9xN7GFPC-hzrZ6QQ0i4iGygbqP2oz6Ovo38bxK3utVeb3eV2y2v7pVm_V2sup442a36jlHemi6mG16w3_FLOmcqm3KVOwy353Z6Xqrotr-uWZg7fl727PFPOlR3HSbnt4Lf5zSD0pVTL892a67urXnclOCllR0JB8X_5CPPhtQMAAA.png","cards/a5-avant-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT55tknYzs7MzIZPd6bgrOzNLiKyd7E-Sra4YLbnwwippKuLFdpKdZDfNbpb9SVPSC2-q3vgDFn-qUqjtjRZFCkVbqVSlFkQFe2GxBW2vFCNeKE2LKE68OA_nPXzv950D7znzu-jttgTPPHLmz-E7fdv3_YwQa00hQsdFqNlY7BFCVNhRq3uL_q5AD9teIeOvdTLeanNX1s1OZAI9NZt31zKTh6rBOpjxlpcV0R_4RG_g7jkVYFs0QOTtANvHxP_c6vvcFq5sadxQUL0WbJ7e8onIYLe13PRaXv3-lt9urjTatVVfHSm4xXwlOz6fG8vPzeWyfrYw508W_UKlOF_MFxYmFwqum1uo5LSgxWURqvhdEV2aK7drFb88lnfdtXF3TPQtdAve2GGxbev2pIa55yZDr6DPoJ8ldof4gxijGFMYxzDew_iYZIbkaZIXSF4ldY3UX1g9WEtYf-D8S3oP6TbiYcIy4aOELyK1UHRi68Q-ZOdlzAbmHOaLjNZIPoD9KvZ3OJuILOqnaIMMHUOfQA8mLmJqmCPYIexR7B9xPiLcT_gU0kNE8qjraGW0r9ATxA8S_5r4bYwNrH5sBdvCLmOfwMkx8BgDt5E-QYuhTaO_i_wB8nnkc8h3UXejllE91C9Qv0VLoxXQ9qJ1iV_AfBzzCCP3kbhOYpPE3yT-IdlLMkrqCqnfsAys17A6WBexZ7E3cTQcG2cvzk9IJ5FfRz6L_CtKA-UtorNEaxjrWEVibWLHGT1A_CTGUxjnMM5jzpO4ROJzrM-QNJRrDN5iqIr-Avolhl8mtkTsKE4Z502cL4OIIvoRR9ixQfhRwjOE64RvMHCAgXUGbiFJSMF7X0K-SkQmYhJ5FmUKZR_K8ygn0KeJv4Nxk51NzPcxvye5m-R-kquk7mKNoE6jycSfJH4YU8L6BusXpD6ke4lsoGyg9qK-gb6O_kMQt0W_sVprrTTqfqNTmul0K7WV9KFapVMt5d3ieLrq1xarnVLOncimveVm1St1Wl0_Pe_V_ZZXmtr_RHZPeaqcK7uum_YawW_r1ILQl9J1v-NVvI636rfawUkpOxgKiv8DMx5wT7UDAAA.png","cards/s5-limousine.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcVRzHXz6bNO3u7E5mYqY703G3ZGaWEImZbCbJprpCQg2erJi2QT2ss9lpdtvsZtk_aXSLeKl6UTyI2qp4CT209Q9UitqilGKpSAXbg0UQoieFqAcxqYjgxMP78L6P3_f3ew--7-JvoqfdEDwze_HPvfd27T68gRBrdSEiZ0WkXlvqEkKU2FOp-kvBaKj32v7ESLDWGvFX66NZNzs1EuqZI567NpI7WQ7XiRF_eVkWvaFP9ITurvUQ3X0hEu-G2D0m_udO35d2cHNH40bC6rVw89SOTyT6243lut_wqw82gmZ9pdasrAbK0GIuN5VbLHmLbjHnTRS9YHKxNOVOF6eKucDzjmVL_piXnSx6atjihoiUgrboO14sNCuloDDmue7apDsmdh1rZ5sTz4nunduz_yvu7zDwOto82iWS99AfxhjGmMV4A-M8xqekR0mfJ32F9B0G7zL4F1YX1gLWH2SiZA6S8RGzRONETxP9AqmBrJHskPyIfTcwa5hFzFcZrpB-CPst7G9xthETKFdR-xk4hzaOFk5cwlQxTewI9jD2DzgfE-0luo70CAkP5XnUp1G_ZuA2-gn0b9C3MDaxerBlbAu7gL2OM07sMWJbSJ-gJlHn0M4R_5D4Z8QvE99COYBSQPFRrqN8h5pBnUA9hNpGv4L5OOYphh4g9SOpbVL_kPqXdDfpPgZvMvg7loH1JlYL6yr2URxwVBwd5xDOBtI68TPELxH_FbmG_A59R-jbxuhgTZNskjzL8LPoH2AsYFzG-ByzROoaqetYXyKpyHfp1xkoo72Cdo3kfSSPkzyNU8A5g3MrjCiiF3GKPZtEHyU6T7RKdINYkViH2M9IElL43teI3yERJ2GSeBF5Bvkw8svI76PNob-H8RP76pgXMG-TPkB6gfQqg39jDaHMocroT6K_gClh3cL6BSmCtJ_EJvImSg_K22gdtO_DuC0FtdVKY6VWDWqt_HyrXaqsZE5WSq1y3nOnJzPloLJUbuXH3alsxl-ul_18q9EOMot-NWj4-ZmjT2QPFmYK4wXXdTN-LfxtrUoY-nymGrT8kt_yV4NGMzzJZ_sjYfF_ofLVKbUDAAA.png","cards/s5-avant.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcVRzHXz6bNO1mdiczMdOd6bhbdmaWEImZ3c1ukuoKCTV4smLaBvWwTnan2W2zm2X_pNFU8VL1ongQtVXxEnpo6x-oFGmLUgqlIkVsDxZBiJ4Uoh7EpCKCsx7eh_d9_L6_33vwfRd_E32dpuC52Yt_7r2_a_fhTYRYawgROitCjfpSjxCizJ5qzVvyxwO91_ZyY_5ae8xbbYxn3MzkWKBnjky4a2NTJyvBOjHmLS_Loj_wib7A3bMRoHcwQPSDALvT4n92-77axa2uxg0F1WvB5pmuT0SHOs3lhtf0ag83_VZjpd6qrvrKyLTvT_hT6WN5P5_O5Scz7vRUPuuX0152yl_MTLql0lS2VEqn1aDFTREq-x0xeHyx2KqW_WJ6wnXX8m5a7DrWybVyL4je7u3Z_xIPrjP8Fto82iVi99EfxRjFmMV4G-M8xhckxkmcJ3GVxF2S90j-hdWDtYD1B6kwqYOkPMQs4Qjh04S_RGoia8TWiX3KvpuYdcxFzDcYrZJ4BPtd7G9xdhA5lGuoQwyfQ8uiBROXMFVMEzuEPYr9A85nhPsJbyA9RnQC5UXUZ1G_ZvgO-gn0b9C3Mbaw-rBlbAu7iL2Bk2XgCQa2kT5HjaHOoZ0j8gmRK0QuE9lGOYBSRPFQbqB8h5pCzaEeQu2gX8V8EvMUIw8R_5H4DvF_iP9LopfEIMlbJH_HMrDewWpjXcM-igOOiqPjHMLZRNogcobIJSK_IteR32fwCIM7GOtY08RaxM4y-jz6xxgLGJcxrmCWiV8nfgPrKyQV-R5DOsMVtNfRrhN7gNhxYqdxijhncG4HEUX0I06xZ4vw44TnCdcIbzKwyMA6Az8jSUjBe98kcpdohKhJ9BXkGeTDyK8hf4Q2h_4hxk_sa2BewLxD4gCJBRKrJP_GGkGZQ5XRn0Z_GVPCuo31C1IIaT_RLeQtlD6U99DW0b4P4rbk11erzZV6za-3C_PtTrm6kjpZLbcrhQl3Op-q-NWlSruQdSczKW-5UfEK7WbHT5W8mt_0CjNHn8ocLM4Us0XXdVNePfht7WoQ-kKq5re9stf2Vv1mKzgpZIZCQfF_WwmMUrUDAAA.png","cards/rs-5-limousine.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbZRzHn37SP2t6yfVu9Ja7HUnJJaGLxF6SNm0ngXWOom-2STeLKGaX5dpka9JwSdpC98I3k8EYiIhOfaEvyl7M4RRk6ibDMZBJUXAIDkGYwsDh1BcW2yGCV-F5Pvx-D9_fF37wfa78Lno6nuDFg1f-2rPdu-vYfYRYbQoRWBeBZmOhSwhRob9WdxbcUb_fM-KMZ9zVdsZZbo7m7NxExmuNZw7PZKaPj9mrmcmVqn9PZ5zFRVn0-bOix3fomvXRbfsIn_ex62XxP3e8X93Bxk5PNuCrV_3ihZ05Ed7d8RabjufUn_TcVnOp0aotu8pIZTxrZ-ezhYozNTU-X56YrBTcsfl8wS6Xs9mJcuFkwc1P2Pak6lvcEYGK2xGDp8qlVq3ilrJjtr1asLOid76T8zxHdO9swHA35m8MvYb2EtqnRLbRD2CkMZ7GeAPjMsZnxEaJXSZ2g9hd4veIb2J1Yc1h_UlKJnWI1DziWYISwbMEbyJ5yBqRNSIfs_crzAZmGfMC6Rqxp0i8TuJbkluIMZQvUBWGLqHl0A5iLGDqmCaJAIk0iR9JfkSwj-A60jRhX7-GuoR6nXQf-mn0DfQtjAekB0n4Z5hEicQ6yTwDBxj4m32bqBHUGbRLhD4k9Dmha4Qeo-xHKaG4KLdRvkNNoY6jHkFdQb-BeRjzDCNPEP2J6BbRf4j-S6yH2CDxr4n_gWVgvYnVxrpJ4iiJhyRVkjrJIyTvI60TukjoE0IPkRvI7zJ4nH3bGGtYU0RaRN4hfQL9KryFMYdxDeM6ZoXoLaK3sb6kZxRJRb5HuoehKto5tFuk-4mcInKWZInk2yS_8cOK6EOcof8RwSLBWYJ1gncYKDOwxsAvSBKSv_UFQt8TDhE2Cb-CPI18DPkc8ntoz6C_j_Eze5uYH2DeJbaf2ByxZeKPsUZQZlBl9OfQz2NKWBtYvyL1Ig0TfoS8idKFchFtDe0HP3QLbmO55i016m6jXZxtdyq1pdRKrdKuFsfsqUKq6tYWqu1i3p7IpZzFZtUptr2Omzrp1F3PKU4_fzR3qDRdypds2045Df_ftWt-9Iuputt2Kk7bWXa9lv9SzO0O-OL_AM_LFS-_AwAA.png","cards/rs-5-avant.png":"https://mediaservice.audi.com/media/fast/v3_x2TYWgbZRjH3_6ytmt6yfVu9Ja7HcnI5UIXib0mTdNNAlbnUJBt0s0igvHaXJNsTRouSVvoPvhlMhgDEZGpoH4oA-cYCjKlk-EYDKQIOgSHIEw_Oaz6wWI7RPAqPO-P53l4nj888H-v_S56u77g5aeu_bV_p2_vqQcIsdISIvS-CLWa1R4hRIWBesOteqNBvX_ELWS9lU7WXWqN5pxcMeu3C9njx7JTp8edlezkci14Z7PuwoIs-oNd0Rso9EwH2OMEiF4MsPcV8T93tV_fxcZuzVgomF4Jkpd290R0X9dfaLm-23jc99qtxWa7vuQpI5WJ2dl8YXI-7006njeZL-Qdd67iOPPuZN4tOnNz-WJurOg6aiBxV4QqXlcMnZktt-sVrzw27jgrE86Y6JvvFnzfFXt2L-BgEvM3ht9Am0b7nNgO-tMYGYyAb2FcxfiCxCiJqyRukrhH8j7JLawerBmsP0nLpI-Snkc8R1gifJ7wLSQfWSO2SuxTDtzFbGLOYl4iUyfxBKk3SX2LvY0oonyJqjB8BS2H9gxGFVPHNEmFSGVI_Yj9CeF-wmtIU0THUVZRF1HXyfSjn0XfQN_G2CQzRCoIm1SZ1Bp2nsEnGfybQ1uoMdRjaFeIXCeyTuQGkUcoR1DKKFWUOyjfoaZRC6gnUJfRb2IexzzHyGPEfyK-Tfwf4v-S6CUxRPJrkn9gGVhvY3WwbpE6SeohtoqtY5_AfoC0RuQykc-IPERuIr_H0GkO7WCsYh0m1ib2LplX0T_CmMG4gbGOWSF-m_gdrK-QVOT7ZHoZrqFdQLtNZoDYGWLnscvY72B_E9gU0Y84x8Am4ecJTxNuMFJmcJbBVQZ_QZKQgnsvEfmeaISoSfQ15CnkU8gXkD9Aexb9Q4yfOdDC_BjzHokjJGZILJF8hDWCcgxVRn8B_SKmhLWB9StSH9JBopvIWyg9KJfRVtF-COxW9ZpLdX-x2fCandJ0p1upL6aX65VOrTTuHJ5I17x6tdYp5Z1iLu0utGpuqeN3vfSc2_B8tzT14snc0fJUOV92HCftNoMf16kHpi-lG17Hrbgdd8nz20GnlNsXCob_A5VC8gG5AwAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a5</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:02.660Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a5</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a6.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/a6-limousine.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAA_1vzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grz9Wu1QZ56rnMhy1ePSvpKdrvVd7gyMAK1MXYByRYGIEE3z8gwWHDACZB5oEN3QniMxkyMzCwVgAZkQwgwMdXWpRTkFiUmKtXnplSkiGoYUAkEGZ3cQ1x9PQJBgCLqOBV6QAAAA","cards/a6-limousine-e-hybrid.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAA_1vzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grD_sm3inPerLXnY9K3VmguHoi28fS4wysQF2MfUCChRFI8P0DEhw2DGASZB7Y0J0gPpMhMwMDawWQEckAAnx8pUU5BYlFibl65ZkpJRmCGgZEAmF2F9cQR0-fYACc3tOF6QAAAA","cards/a6-avant.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbdRTHf_2kXdf03qT3lt4m2TWR3NxYOrLd_G0zF7VDqk9u2HUiPmQ3vbdttiYN6U2sdg--DH1xCMrwDzKd-qLDKZOh3fAvyIaoqA_KFHQ-KVYEldU_OLzdy5dzDuf7PefA95z5VfR12oIH9p35Y_SvbdsP_oAQqy0hAi-KQKu50COEcBioN-wFd7efj5p2KeOuehm729qds3ITGbtkd-2ml5maLZZzmcIBK2MvLYVFv08UfT6954QPvT0-hK77sH2vuIFbwjfU39nKyQb87lU_uH-LJ0LDnfZSy27bjV1td6W13Fypd11lrJibnLSyc25-3innS-WSWygVrXmnli3N5Z1yrTZXKkw6xXlX9SUuiYDjdsTQkVp1pe641WzBslZLVlZsm28W7YcXRO_W-iRv56arjDyBNoP2Bto5ohDdS2yc2BSxp4i9SuxtEhkSr5C4QOILkldI_o4hMI5g_IZ5nXSe9FHEHQRlgscJvovUJqwRWSNylh0fozfRa-iPM14ncSupJ0l9jrmJ2IVyEXWYkbNoE2j-xAV0FX0M_W5SAVLjpK5gvkmwn-DLSLcg3UaogOKhLqNeRttJ9CjRT4j-SWwDY4BUmJRBqkrqFGaWwX0MXkN6CzWCOo32EvLryOvI55GvoexBqaLYKB-hfIaaRi2i7kftEL2Afg_6MfR1xnYS_5b4JvF_if9HopfEEMlLJH_BiGGcxPAwLpKaJbWJqWJGMfdjfo90GvkF5HPIPxNuEn6OoVmG_sEoE1kh8izjh4meJnYfsfPE1tEd4u8T_xDjPSSF8DcMDzCyiPYY2geMniRyHLOK-QzmZd-piH7EMQY2CN5FcIZgg-B3DB5mcI3BH5EkJP_YE8hfEZIJ6YQeITxF-CDhRwmfQpsm-jyxq-xoob-G_iWJPSQOkeiS_BtjDGUaVSZ6L9GH0CWMTzF-Qgog3Uxog_AGSh_K02hraF9vOdptduvt5WbDbXqVGa_j1JfTD9Ydb7FSsMql9KJbX1j0KnlrIpe2l1qLdsVrd9z0nN1w23Zl6tCB3J3VqWq-allW2m76T-fVfetX0g3Xsx3bs7tue8WvVHLDAb_5f5PzKAm8AwAA.png","cards/a6-avant-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcBRTGJ79t_nQzs5OZkMnOdNyVnZk1RLad3Ww2SdsVU0r01FbSVMTDdrI7SbZmN8vu7JqSHrwUvVgEpfgHqVa91GIthWJTqf9AKkUFe1CqoPWkGPGgNBZRnPTy8d7jfd97D753_nehu90UeHLf-T-H_-7pO_wTgrDaEITIm0KkUV_sEgShwvZqzVv0d4X5sOMVMv5qkPE6jV05NzeR8Qpex6sHmem58alcJn_IzXjLy7LQGxKF7pDedSqEbV0hxP4LoW-vcA-3hO-pX9nKyUbC7tUweGKLJ8QG283lhtf0ajubfquxUm9VO74y4vmTCxNevlzxymV3IpcvlAvZQnnCX_DdyqTruwvZyth8fmpSDSWuC5GK3xYGjs2XWtWKX8rmXXe14GaFnoX6uJc9LmzbWp_UMPfdZugFtFm099EuoYO-F2MUYxrjJYxzGB-QzJB8h-RVkjdJ3SL1F1YX1jGsP0hDej_pFsLDRCWiJ4leQ2wia8TXiF9gx-eYdcx5zOcZrZLcg_0i9tc4mwg7UT5EHWToAtoEWjhxEVPFHMF8FDuCPYp9C-ci0V6ibyM-gPgQsTzKGmoJ9QZaAv0p9BvodzA2sHqxZWwLex77DM4e-vfRfwfxCmocdQbtLaT3kNaRLiPdRdmNUkLxUD5D-Qo1jTqOehC1jX4V8wDmCcx1Rh4k8T2JTRL_kPiXZDfJAVLXSf2GZWCdxgqwrmHPYW_iqDg6zkGcHxHPIr2BdAnpV-Q68msMzDFQxZoi3iL-KqNH0c9iPI5xGWMds0LiYxKfYn2EqCB_x2AfQ0toz6F9wvBp4idxSjiv4HwROhWhF-EE2zeIPkJ0lmiN6A_0H6V_jf6fEUXE8NhTSDeJScRMYs8gTyMfRn4W-QzaDPrrGLfZ0cB8F_MbkrtJHiHZIXUXawRlBlVCfwz9OKaI9SXWL4g9iPcT20DeQOlGeRltDe3bLUf79U61uVKv-fWgOBu0K9WV9NPVSrBUzLtThfSSX11cCopjoXfT3nJjySsGzbafLns1v-kVp48cyu0vTZfGSq7rpr16-HRBNbR-MV3zA6_iBV7Hb7bCSjE3GAmb_wc7wb6WvAMAAA.png","cards/a6-allroad.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2gcdRDHf_lc2qSX3dvshmxvt-udZHev4eTau2tyl0ROuFhKfbHFpBbx4brpbnJXc5fj_sTUiPgS9EVREKmWUmj1RYtVKkXa4l-UVlHEPihV0PqkGPFB2yiiuPHh9-E3w8x3ZmDm3K9iS7cleHj63O_b_9zaP_sDQqw0hYicFZFmY6FHCOGzrVb3FoLdob19p1fIBCudjLfc3J3P5osZr-AtLraWPD9TPjQ-uZIZO1jOhB5F9IWpYkso0PN8iMgfIRRC9E-J_7kpvbaJa5s2uUgYvRJ-HtrME7Ghbmux6bW8-q5W0G4uNdq15UAdLeb8-fFCIe8Xvblx35_IT3jFsIOJ-VwufEf9IDuXDwq5OS2UuCoiftAVg8fmKu2aH1RyY9nsSiGbE1vnG1Vv8bjo3RyAtMIdNxl-Dn0G_U30Cxhg3IuZxixjvoD5GuY7JDMkXyV5meR1Rm4wcgu7B_sY9m-4_5LaS6qNuI-oTHSN6LtILRSd-Crx8-z4BKuBNYf1DOkaybtx1nC-xN1A7EK9gjbE8Hn0InpYcQFLwxrF2o8TwUnj3MB9i2gf0VeQdiLdQ2wM9TG0JtrH6IMYj2B8hnEbcx27D0fBsXEqOKdxcwxMM3Ab6W20ONo-9LPIbyB_inwR-RbqFGoF1UP9CPULtBRaCe0AWhfjMtb9WE9gXWL0LhLfktgg8TeJf0j2khxk5Cojv2Cb2C9id7Cv4BzC2cDVcA3cA7jfI51BPol8AflnlAbKSQZnGTyFPUm8Tfxl0kcwzmAexryIeQnLJ_E-iQ-x30NSUb5hqJfhKvrT6B-QPkF8DbeC-xLuNUQPog_xONvWiU4TnSFaJ_odA0cYWGXgRyQJKRz2WeTrxGRiFrEnUcoosyhPoZxG349xCvMmO5pYr2N9RXKK5GGSy4z8hT2Kug9NxngA4ziWhP059k9I_Uh3EltHWUftQT2Bvor-dbh0C0FjudZaatSDRqc00-n6taXUozW_Uy2NZScLqWpQW6h2SnuyxXzKW2xWvVKn1Q1SR7160PJK5QcP5vdWypU9lWw2m_Ia4dl1auHql1L1oOP5XsdbDlrt0FPKD0XC4P8AdU8vRb4DAAA.png","cards/a6-allroad-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TcWgbdRTHf_1kbbf0kutd6TV3OxPJXbJSyXZN2mStREgdo_7jBm0nopBde5cms0lDknYdFfGfwv5RFESmQwZT_GOOTRkM6WQ6BjKVibg_lCno_Euh6h-O1SGCV__58N7jvS-8x_dd_F10r7QEz01d_Gvo757dsz8jxFpTiNC7ItRsLHYJITz21Oruon8gyIf2ufmMv9bJuKvNA1knW8i4eXdpqbXsepnS3PjEWmbsaCkTVGTRG4yK7kCg6_UAofsBZALsnhT_c0d6Ywdf7OSMhoLutSB4dmdORAdWWktNt-XW97f8dnO50a6t-srw6HwlO-FlC4VKZTw3X3Encp6TP5iv5PwgyBYqruMtLBzM5tVA4pYIef6K6D8xX27XPL88OuY4a3lnVPRUGlU3e0rs2lmA5BCP3GPwNbQZtA_RrqCD_iTGCMYUxhsYFzA-JpEhcYHENRJ3SN4leR-rC-sE1p-kIX2IdBvxFOEI4Q3C15FayBqxdWKX2fs5ZgNzHvMVRmokHsfewP6G1DZiP8onqAMMXkYroJUwFjFVzGHMaewQ9gj2XVIfEe4l_B7SPqQniI6hrKM-j_oZWhz9BfSv0B9gbGH1YsvYFvY89jlSOfqm6XuAtIkaQz2M9j6RS0S-JHKVyEOUSZQyiotyE-Vr1DTqOOoR1JPo1zCfxnwJc5Phx4j_QHyb-D_E_yXRTaKf5C2Sf2AZWG9idbCuY89hb5NSSemkjpD6Cek8kbNErhD5DbmBfJb-OfqDu00QaxN7m5Hj6OcxnsG4irGJ6RG_Qfwm1qdICvL3DOxisIp2Gu0GI2eIbZAqk3qL1O3Aq4hexIvs2SI8RXiGcJ3wj_Qdp2-dvl-QJKRg2VeJ3CEaIWoSfRm5hDyLfBr5HNo0-jsY99jbxPwA81sSkySOkVgl-RBrGOUwqow-i34KU8K6jfUrUg_So0S3kLdQulDOoK2jfReYbtFvrNZay4263-gUZzorXm05fbLmdarFMWcin676tcVqp5hzCtm0u9SsusVOa8VPL7h1v-UWS8eOZg-VS-Vc2XGctNsI3q5TC6xfTNf9juu5HXfVb7WDSjE7EAqa_wMgAk92vgMAAA.png","cards/s6-limousine-tdi.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAAAFvzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grT4bQBMaSh0LzF1-XPbEn-OZsmdyGjwysQF2MCkCC-ROQ4NsKJDiCGcAkyDwfELEWxGeyYmZgYK0AMiIZQICPr7QopyCxKDFXrzwzpSRDUMOASCDM7uIa4ujpEwwAXC-qpukAAAA","cards/s6-avant-tdi.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAAAFvzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grT4lowt1rKVsi7V3ET3OpzvU7GvFoFQMrUBejApBg_gQk-LYCCY5gBjAJMs8HRKwF8ZmsmBkYWCuAjEgGEODjKy3KKUgsSszVK89MKckQ1DAgEgizu7iGOHr6BAMASb3nlekAAAA","cards/rs-6-avant.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAAAFvzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grz6_lrV2KAXbZb1UOms9v_6_FlHzlIgMrUBejApBg_gQk-LYCCY5gBjAJMs8HRKwF8ZmsmBkYWCuAjEgGEODjKy3KKUgsSszVK89MKckQ1DAgEgizu7iGOHr6BAMAa2HQ2ukAAAA","cards/rs-6-avant-performance.png":"https://mediaservice.audi.com/media/fast/H4sIAAAAAAAAAFvzloG1tIiBOTrayfuvpGh6-m1zJgaGigIGBgZGoDhTtNOaz-I_2DhCHsCEtzEwF-SlMwJZKUycmbmJ6an6QD4_I3taTmV-aUkxO0grT8ga14XrXsyb0lkjNTX87zSd63_2azGwAnUxKgAJ5k9Agm8rkOAIZgCTIPN8QMRaEJ_JipmBgbUCyIhkAAE-vtKinILEosRcvfLMlJIMQQ0DIoEwu4triKOnTzAAUztkyekAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a6</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:07.668Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a6</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a6etron.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/a6-avant-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcBRDHN79rPrrZu81uyOb2ut5pdveMkbN730nlxCsSS5FWiaaID9dNbnN3MXc5LntnpBVUKPiiKIIWoURK6YMGixSK1KKtXxQFH-xLLT60FaFiRFBoFVHc-PJjZpj5DzPMbP4q9Hc7As_s3fxj_M-BoSevIwjrbUEInRBC7VatTxCEKjsbTbfm7Q788Sm3kPLW_ZTba-_OOJliqlzw_M5qq9xzW36q_FQ-vZ6azZdT7sqKLAwG1UJ_oNF3IMCOwQCRcwGGDgn_c1v9hW1c2vZxQkH2emA8vV0nREa7nZW223GbD3S8tfZqa63R85TJ6aWiU83PLC1OZ2fcpXRmKVtYKGa8fCGbzhRzmYVc2ssWpxc9NZD4UghVva4wsrxQWWtUvUo65zjrBSctDNTqeXfBFXZsz8A9j3HXDcZeR5tDexvtLLqI_i-xMrE3iG0S-wjjOIkUifdIfEziChNXmbiNCaaIuYz5G8kEyf0IDyOGEMOIx5A6SBvIGtEjRM-w6yuMFsYCxqtMNUg8iPUm9j7sOwgZlAuoo4ydQSuiBX1rGCrGJMY-rBDWFNY17A8RBxFPId2LVEB6iEgOdRX1AloI_Vn0b9B_x5KxbKw8VgVrA-tr7BzDexm-jbKFGkWdRTtN-APC5wmfI3ISRULZg1JBcVE-R_kW9SBqF_0ixgGMo0zeT_wa8TvE_yb-D4khEiNMXGbiF8wY5luYPuYnWPNYt7BVbB17P_ZB7OtIpwi_S_gs4Z-RW4y8jDlDdI3oO0wdRj9J7BCx8xhV4heJf0b8J8xPkRTkq0yFGKujvYJ2ifE-ostEj2FXsL9AGEQ4ys6biI8iziE2EX9g-DDDRxi-iSQhTSMFM75G-AqRMJEXkcvI88gvIW9w32W0WfQTxG6wq43xPsZ3JPaQ6DHxF-YkyiyqjP4E-vMYEuYtpAGku4lsIW-h9KMcRwlW9yPa98Gt1bxWrxF8QtNr-aU5v1ttrCafa1T9einnzBSSda9Rq_ulrFPMJN2Vdt0t-Z2ul1x0m17HLZXnH888UilXshXHcZJuK3g4vxFcfCnZ9Hy36vpuz-usBZFSZjQUJP8HmeY5vLgDAAA.png","cards/a6-sportback-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbdRjHb5-0a3e95HpXes1lZzJyd1mtxF3SNGknEVOljr3YlGqH-CL7ZTmT1CYNaVIrm6DCwDeKIugYSGUMX2hxyGCIDt38R1HwhXszhy-2iTCxIihsiiheffPheR6e5_vwPDzPxq9Sf68j8eTsxh9jf-4cfOw6krTWlqTQaSnUbtV2SJJUZVejKWr-vsAf2yvyaX-tmxar7X1ZL1tIl_J-t7Pcmp9Nlx6fyqyl56bm0mJpSZUGglKpPxDYcShA30CAyIUAg0ek_7kt_dw2Lm_7eKEgey0wntiukyIjvc5SW3RE896Ov9Jebq00Vn1tPCOyvqhWRSV7TPj-U5nCZNUrVDK56UrFn_Fmstnc9KQ3lS_ogcSXUqjq96ThxUp5pVH1y5mc563lvYy0s1YXoiKkvu0B2PMgd91g9FWMeYw3Mc5jypj_EisRe43YBrEPsU6RSJN4l8THJK6QvEryNjbYMvYi9m-kEqQOIj2AHEIOI59E6aCsoxpEjxM9x-6vsFpYFayXmWiQuA_nddwDuHeQsmgX0UcYPYdRwAj61rB0rHGsAzghnAmca7gfIA8gn0XZi5JHuZ9IDr2FfhEjhPk05jeYv-OoOEmcHE4ZZx3na9wcQ7MM3UbbQo-iz2G8Q_h9wpuELxA5g6ag7Ucrowm0z9G-RT-M3sO8hHUI6wTj9xC_RvwO8b-J_0NikMQwyU2Sv2DHsN_A7mJ_grOAcwtXxzVxD-Iexr2Ocpbw24TPE_4ZtcXwi9gzRFeInmbiKOYZYkeIfYRVJX6J-GfEf8L-FEVDvcpEH6N1jJcwLjMWIrpI9CRuGfcLpAGkE-y6ifww8jxyE_kHho4ydJyhmygKyjRKMOMrhK8QCRN5HrWEuoD6Auo6d29izGG-RewGu9tY72F9R2I_iVWSf2GPo82hq5iPYj6LpWDfQtmJsofIFuoWWj_aKbRgdT9ifB_cWs1vrTaCN2j6rW5xvturNpZTzzSq3Xox583kU3W_Uat3i5NeIZsSS-26KHY7PT91TDT9jiiWFh7JPlQulSfLnuelRCv4tm4juPhiqul3RVV0xarfWQkixexIKEj-D0PNpcK1AwAA.png","cards/s6-avant-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tf2gbBRTHr5-sP5Zecr10veayMxm5u1grsZefbScR02kp_tEp1RYRiRfvSDKbNCTXrNApogz8R9F_ZIpjIGV_zKKCMmSKbo7KUPzD-c_cX3MiKFQFhU0Rxav_fHjv8d4Xvo_3tn8R-tc7Ak_Mbf8x_ufA0KM3EISNtiAETguBdqvWJwiCw_5G0665U34-PmkX0-6Gl7Z77amslZ1Ol4uu11lrlXt2y0uXHytkNtLzhXLaXl2VhEF_Wuj3NfoWfewb9BE-72NoRfife-rP7uHSXo4V8Ls3_ODxvTkhPLreWW3bHbt5T8ftttda3UbPlSccK-9Wp6u53EzRstxiwc7NWDNF27Xz-YxbdJ1qNZ-ddZxMxJfYEQKOuy6MHKtWug3HrWTylrVRtDLCQK1e6Lozwr49Dxw6wh2bjL2KsoTyFsoHqEHUf4nNEXuN2Daxj9BOkZgicY7ExySukrxG8hZ6H_oB9BX030glSS0izBEMEAwRPInYQTyDpBDdJPoeB79Aa6FV0V5mskHiXowXMRcwbyMUkD8hMsrYWZQcyv3EamgRtAm0BYwAxiTGdcz3CQ4S3EK8E7GIeB_hPJEniXzO2A7qM6hfof6OIWGYGAWMCsYWxpeYeYYXGL6FvEskSmQe5SyhdwldIHSe8NvIIvJh5AqyjXwZ-RsiR4kcR72Itoh2gom7iV8nfpv438T_ITFEYoTkFZK_osfQX0f30D_FWMYEM4KpYj6EeRTzBuIWoTcIfUjoZ6QWIzX0WaJdom8y-RTqOWIrxC6gOcQvEr9M_Ef0zxBlpGscGGCsjvISyiXG-4geI3oSs4L5NcIgwgn23yT4IMElgk2COwxXGd5k-CaiiDiD6Ht8hdC3hEOEn0cqIy0jvYB0hruuoMyjnib2PQfbaO-gXSVxmESP5F_oE8jzRCTUR1CfQxPRf0IcQDxEeBdpF7kf-RSyv7ofUL7zb63mtnoN_xOabssrLXnrTmMtdbzhePVS3potpupuo1b3SjlrOpuyV9t1u-R11t3U03bT7dil8vLD2Qcq5UquYllWym75D-c1_IsvpZquZzu2Z_fcTtevlLKjAb_5P23B6OC4AwAA.png","cards/s6-sportback-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tf2gbBRTHr5-sP5Zecr2rveayMxm5u6xWYi8_mnSTiC1ain90SrVFROKldySZTRqSa1foFFEG_qPoPzKHMpCyP7aigjJERTdGpSj-4fxn7q85ERSqgsKmiOLVfz6893jvC9_He9u_CL1rHYGnZrb_GP2zb-DxmwjCRlsQQmeFULtV6xEEweVgo-nUvIkgHz3iFDPehp9x1tsTOTtXykwXPb-z2lqYyUw_MZndyMxOzmaclRVJ6A9Ghd5AoGc-wIH-ANFLAQaWhP-5L_3cPq7s59ihoHsjCJ7cnxOiw2udlbbTcZr3dbxue7XVbax78phbLLhTVc_NVyeLWbe0nHWqOXvKdUpOseRl81VnsuiW3PyyEkjsCCHXWxOGTlQr3YbrVbIF294o2lmhr1Z3ut6UcGDfAIeHuHuTkddQF1DfQv0ALYz2L_EZ4q8T3yb-EfoZkhMkL5D8hOQ1UtdJ3cbowbgLYwnjN9Ip0vMIM4RDhCOETyN2EM8hqcQ2ib3HoS_QW-hV9FcYb5C8H_MlrDmsOwiTyJ-iDDNyHjWP-iDxGrqCPoY-hxnCHMe8gfU-4X7CW4hHEIuIDxAtoDyNssPIDtqzaF-h_Y4pYRqYBcwK5hbml1gFBucYvI28hxJDmUU9T-RdIrtELhF9B1lEPoZcQXaQryJ_g3Ic5STaZfR59FOM3UviBok7JP4m8Q_JAZJDpHZJ_YoRx3gDw8f4DHMRCywFS8N6BOs41k3ELSJvEvmQyM9ILYZqGEeJdYmdZfwZtAvEl4h_jO6SuEziKokfMT5HlJGuMx5ipI76MuoVRnuInSB2GquC9TVCP8IpDt4i_DDhBcJNwjsMVhncZPAWoog4hRh4fJXIt0QjRF9AmkZaRHoR6Rz37KLOor1N_HsOtdEvol8jeYzkOqm_MMaQZ1EktMfQnkcXMX5C7EM8THQPaQ-5F_kMcrC6H1C_C26t5rXWG8EbNL2WX17w19zGavpkw_Xr5YJ9tJiue41a3S_n7VIu7ay0607Z76x56WWn6XWc8vTio7mHKtOVfMW27bTTCr7NbwQXX043Pd9xHd9Z9zrdoFLODYeC5v8AfCg1VrUDAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/a6etron</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:12.738Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=a6etron</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/etrongt.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/e-tron-gt-quattro.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGH4XjRqu9uj7VdK8UFWr2dj9dMP95Rw8AKNIpxPpBg0QISfL-ABIcHA5gEWZIJIk6C-EwWzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggEPp39D5gAAAA","cards/s-e-tron-gt.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGH4fw-8yOtK66VHIncNfnoyz2poa3MPgysQKMY5wMJFi0gwfcLSHB4MIBJkCWZIOIkiM9kwczAwFoBZEQygAAfX2lRTkFiUWKuXkpqUmm6oIYBkUCY3cU1xNHTJxgAS9uEpOYAAAA","cards/rs-e-tron-gt.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4zMBfkpTMCWSlMnJm5iemp-kC-uFBaTmV-aUmxvpGBkbluaklRfh4_IztUkB2ompGHodbmdcCxdyuW_15yMHHCJLV5Cy3j6hhYgUYxzgcSLFpAgu8XkODwYACTIEsyQcRJEJ_JgpmBgbUCyIhkAAE-vtKinILEosRcvZTUpNJ0QQ0DIoEwu4triKOnTzAA1AXze-YAAAA","cards/rs-e-tron-gt-performance.png":"https://mediaservice.audi.com/media/fast/v3_x2Sb2gbZRzHn37Sdl2TS3opvfbSkBu5XJwdsZc_bVIlssjAIQ6K65SxF9mz5drcaK7xcqkZ842C4BsVEWTvCjJ8oZs4Xw0nA5kKRRhMfSFDUYcvJkwRB8MpiJe9-fD78_194eH5XvxdjPV9wYmnLt6b_Xt8Yu1nhBh0hYjMikjX2xgRQrTY63bkhrMY9rMHnMDf8grOICjI7e5iyS5VCw9HT68VVhuFxrGl4qBQeaZYkJubCbEnPBdjocnITojRhRDxf0JMHBYPObR3h9gd9tQioXoQFseHdyI-3fc3u9KXncd8p9fd8nrutqPud8pVe12WZLV0ulheqZVay0V7Wa5Xa0srS3alGOJUOVw6ydDivIi0nL6YOnOq2XNbTrNYse3Bsl0U4-u1rl9ridHhC9g3SqaIdhTtMtoVdAX9P1IfkLqC8SHGVYwbGN-QvUn2PuYIZhTzEOZxzL_I6yy8Rf4s4iAxn9gOCY25y8x_RdojfZL0Gyy4WPcQFdTPSKrMXEBbJLVOboHcLawZrBewPmYyyuQFYgViT6IExEP9EZJnSH7KzHfoHvrX6H9iTpBLkGuS2yF3CesJooeJ3kd7H2UXNYbaRJWoX5Lsowfo10k_x_4DZH4k84DMvxgTGFMY-8j-gfkO5iuY1zCvk_sNK4n1CNYq1k8o51F-IOEx9Qmpc8z1SV0l8T3TZ5lpo72O9jmzd5h7DeNlrBNYL2LtIvaw9zaTzzLZI_ooUUn0HNHbxBRiH6GcRHkT5VviCokGySPob5P6hfku6UtkrmE8TvYBZhb1IPoa-qukxzDvEJsnfpfEXdRx1HdR30P9Fe2L8JM3HG_bDSPYcbygfjTot9yt_EtuK2jXK_bKcr7tuBvtoF62q6W83Oy2ZT3w-07-tOw4vqw3nl8tHWo2muWmbdt56YVRD9wwavV8xwlkSwZy2_F74aRemo6E4v8B4IOXyjIDAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/etrongt</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:49.715Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=etrongt</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/f1.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/audi-r26.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjD0CK89NsGXslvP2aeuao66f8-K6u9DgzMDAzsDQwMLBYMIMAnXFqUU5BYlJirV5RaXJCfV5xZliqoYUAkEGZ3cQ1x9PQJBgBHdTswzwAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/f1</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:58.393Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=f1</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/nuvolari.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/audi-nuvolari.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGLYwMBfkpTMCWSlMnJm5iemp-kC-uFRBUX5KaXJJSmpJYmZOsX5afooulM3PyIcqyQ7UzMjDEBjWe-dDzqpFyy9ofdnj-Hin56m76xmYGRjYGxgYWCwYQIBPuLQopyCxKDFXryi1uCA_rzizLFVQw4BIIMzu4hri6OkTDAD_J8cizwAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/nuvolari</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:53.952Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=nuvolari</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q3.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q3-suv.png":"https://mediaservice.audi.com/media/fast/v3_x2TW2gcdRSH__22adrN7mxmQqY7kzEjmd0xiayZvWQ3qSwYKRH6ULUxVVHYTrKzyYbsZt3Mxpj6oILYlxYfWqsVaUl9sValREOhRaXRIgoqIiit4OXJS0TESxUfdOLLxzmH8zsXOOf8z6Kt1RQ8dOf533b_tWPnfd8gxHJDiNCqCDXqM9uEEGV2VWvujDcU-LvtR7Ipb9lPuUuNoYyTKaTGJrPZfGo8m0658_Ope7MTkwdT---KifZAKdoC_bbrAUI_BZBCAXY2xf_cqry6hdNbPk4oyF4OjAe3dELqajXnG27Trd3W9BYbC_XF6pIn9-enC-VCrpAv5Nx0biSbH3GGR0eGc9NuJjc65Xjl0dzUcMXzRpSgxAciVPZaonNuqrRYLXuldM5xlvNOWuyozE25KzNi-9b8DJzjpgrdz6JOoJ5EXWPgJNpb6IPoY-jH0c-hX6TnX4xTmCnM1zAvYX5K3zX6_sASWBWsX7B17CHsfYg7CEcJv02kibSXmEr8SeJv0HMVo44xhXGUwSrm7SQ-IXkDoSEyiAeQLyN_iNKG0kX3cdQCegVDwegnESIxSOIayQuE2wm_TKSAlENeQamjrKOqaGW0j9B-JxEjsULiNIk1kmk69tHxJ5E3UcZRz6JeJfo60StE15FWkdPIe5BLyBeRN5A_RrFR8ih3o7ToPop2CWM_xmH6b6X3Or036P0HcztmJ-bN9P2KpWM9h-VjXcZ6n8QkAxdIKiQ1kl8TPUN0jegPxOrEXqRzks4NBs4QGyG-SPwUg4fQVtHvR19HD3qV6b2C9Q6xL1G-petHumdRj6C-y8AG8TniT2NWMJ8iWSL5Asn3EO2Ix9m1SfgA4Rrh04TPEv6KjkN0HKbjOyIRIq8QCbY-RvRzpCjSw0g-0hNIx4iNEXsG7SV6GhivYnyGuQdzib6_sfqRx1GiaAfQHsOIYH1P8giRENIJpE1im8htyM9zywnUL4Kjm_HqS9XmQr3m1f3ihN8qVxfsR6tlf7aYc0bz9qxXnZn1i1mnkLHd-casW_SbLc-edmte0y2OHbwns7c0VsqWHMex3XrwdX41OP2iXfN8t-z67pLXXAwixUxXKEj-D7iZcKa9AwAA.png","cards/q3-suv-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWhbZRjH3_1i1y5NTnpObZqTnvWMnuTYVuJOkjbZJgEjo4IX0612IgrZaXJOm9KkWb6s1AsdiLvZ8GJanUhH541zTkZxDOYXmw5RUVBB2QQ_riZWRCZO8WKeePPjfV6e__O8z8P_Pfub6GrVBY_ff_bm4N9bex75ESGWa0L41oWvVp3bIoQosa1cseecnV48aB5OJ5zlZsJu13amrFQ2kZ9JpzOJqXQyYS8uJvanp2cOJvY9EBLdnlJ0efot1z34fvUg-Tz01MX_7FRe72CtE2P5vOxl7_BYRyek_lZ9sWbX7co9dadRW6o2ym1HHp11J5PpSSvtZqxi0Som3ZSdzRQnMsndzq6iO1m0s0U3mXWTilfiE-ErOS3RtzBbaJRLTiE5YVnLGSsptroLs_bhZXFH5_2MDLLdZeAFwtOEVwlvMLaK-g7RcaJ5oieIniF6kaHbaCfRE-hvoV9C_5qRa4z8iSEwXIzfMbdjWpgHEPfhD-J_n0AdaS-hMJFnibzN0FW0Ktos2jHGy-j3EvuS-C2EikjhbVl-F_lT5Nso_QycIJwl6qIpaKPEfMTGiV0jfh5_N_7XCWSRJpBXUKooRxi4gVpC_Qz1JrEQsTaxNWIbxJP0PkjvXwQ2UKYInyZ8leA5gpcJXkBaR04i70EuIF9EvoL8BYqJkkF5CKXFwDHUS2j70FYYvZvh6wzfYvhf9B70PvQdjPyBEcV4CaOJ8R7Gx8RmGDtPXCGuEv-B4CmCGwR_IVQl9Cp9M_R9ztgpQruINIicZPwQ6jrRR4leIOr1KjF8GeMDQt-h_MSdZxiYJ3yU8IeMXSGyQOQ5dBf9CPEC8VeIf4ToRjzNtk38B_BX8K_hP43_e3oP0btC788EAgTeIOBNfZzgN0hBpCeQqkjPIB0nlCf0POprDNXQ3kT7Cn0PepuRfzBGkadQgqj7UZ9CC2DcIH6UgA9pFWmT0CZyF_LL3PUi4W8908051Xa5vlStONVmbrrZKpWXzCfLpeZ8bsLanTHnnfLcfDOXtrIp016szdu5Zr3lmEW74tTtXP7gw6m9hXwhXbAsy7Sr3q9rlj3r58yK07RLdtNuO_WGd5NL9fu85P8AnNfiob0DAAA.png","cards/q3-sportback.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWgcVRiGT59tmnazO5uZkOnOZM1AZmdNImtmf9hNKgum1AgFrTZGLV5sJ5nZZEN2s25m01h7oaLYmxYvWqsViaa90bZKiYZCi4rRggqliKC0gj9XihERf6p4oRNvHs57-N7v-w685_zPoq3VFDy2-_xvO__atv2hbxFiqSFE6KwINerTW4QQLjuqNWfaGwr0TuvxXNpb8tPOYmMoa2eL6dGJXK6QHstl0s7cXPrB3Pju9P33xkR7YBRtgX3LzQChnwJIoQDbm-J_bjZe2cTypsYOBdVLweHApk9IXa3mXMNpOrU7m95CY76-UF305P4pJ5sfmbIrw1N2ziu4U8MFzxsuDmcKjp3JuSP5fHHScQOtBC0-ESHXa4nO2cnyQtX1ypm8bS8V7IzYVpmtO4enxdbN9Rk4x20Vul9AHUc9hbrKwCm0d9EH0UfRT6C_iX6Jnn9JnMZIY1zAuIxxnb4b9P2BKTArmL-Q0kkNkdqLuJtwlPB7RJpIe4ipxJ8m_jY9V0nUSUySOMZgFeMuktewbiE0RBbxKPIV5E9R2lC66D6BWkSvkFBI9JMMkRwkeQPrIuF2wmeJFJHyyIdR6ihrqCqai_YZ2u8kYyQPkVwmuYqVoWMvHX8SeQdlDPUM6lWibxG9TnQNaQU5g7wLuYx8CXkd-RpKCqWAsg-lRfcxtMsk7iNxhP476L1J7y16_8HYitGJYdL3K6aO-SKmj3kF82OSEwxcxFKwNKxviL5OdJXoj8TqxF6hc4LOdQZeIzZMfIH4aQYPoq2gP4K-hh7Mcun9EPN92u4h9hXKd3Q9S_cM6lHUDxhYJz5L_DmMCsYzWGWsl7E-QrQjjrBjg_B-wjXCy4TPEP6ajoN0PEnH90QiRN4gEjz8ONEvkKJIB5B8pKeQjhMbJfY82qv0NEicI_E5xi6MRfr-xuxHHkOJou1He4JEBPMHrKNEQkgnkTaIbSC3Ib_E7SdRvwxyN-3VF6vN-XrNq_ulcb_lVudTh6quP1PK2yOF1IxXnZ7xSzm7mE05c40Zp-Q3W15qyql5Tac0-vAD2T3l0XKubNt2yqkH_86vBukvpWqe77iO7yx6zYXgppTtCgXF_wGLJubTvwMAAA.png","cards/q3-sportback-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2TXWhbZRjH3_1i1y5NTnpOSZqTnvVATk5sK3EnHybtJGDGqODFdKtVRCE7XU6alCbN8mWlXuhQ3M2GF9PqRDo7b9SpjOIYzC-cDlEZooKyCX5cTayITJzixTzx5sfzPDz_532fl_975jfR12kKHt5z5vrI39sH7v8RIVYaQnheEZ5GfWGbEKLEjmrNXnB2ufmIeTidcFbaCbvb2JWyUrlEYS6dziZm0smEvbSU2J-e3ZPYd3dA9LtC0efKt1114fnVheRxMdAU_7M3eKOH9V6O5XG7V9zgoZ5OSMOd5lLDbtq125tOq7Fcb1W7jjyeSycztjWdvaM8nbOTpalsbtrJJFPpXNZxw6RzaH4qV06XpxV3xKfCU3I6YmhxvtiqlpxiMmNZK1krKbaXF-v24RVxS-_6REfYWSb4LKFZQmuENplYQ32HyCSRApETRF4ncp7Rm2gn0RPob6JfQP-a6BWif2IIjDLG78R3EreIH0DchdeP9318TaS9BEKEnyT8NqOX0Opo82jHmKyi30nsMuYNhIpI4T6y_C7yZ8g3UYYJniCUI1JGU9DGiXmITRK7gnkWbz_eV_HlkDLIqyg1lCMEr6GWUD9HvU4sQKxLbJ3YJmaSwXsY_AvfJsoModOELuF_C_-X-M8hbSAnkXcjF5HPI19EvowSR8mi3IvSIXgM9QLaPrRVxm9j7CpjNxj7F30AfQjdIPoHRgTjeYw2xnsYnxCbY-IspoKpYv6A_xT-Tfy_EKgTeImhOYa-YOIUgSnCLcInmTyIukHkQSLniLhnlRj7COMDAt-h_MTwUwQrhI4S-pCJi4QXCT-NXkY_glnEfBHzY0Q_4nF2bOE9gLeGdx3vabzfM3iQwVUGf8bnw_caPnfr4_i_QfIjPYJUR3oC6TiBAoFnUF9mtIH2BtpX6LvRu0T_wRhHnkHxo-5HfQzNh3EN8yg-D9Ia0haBLeQ-5Be49TlC37qmW3Dq3WpzuV5z6u38bLtTqi7HH62W2pV8xrVtvOJUFyrtfNrKpeL2UqNi59vNjhM_ZNecpp0vPHBfam-xUEwXLcuK23X307WrrvXz8ZrTtkt22-46zZZbyaeGPW7zf8IiF7y8AwAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q3</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:16.643Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q3</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q4.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q4-suv-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbZRiG_z5xu9scJjuzbHYnO2ZKJgnr2Ngkm002lYCpB2hBtK0tniBOkkk2ZZNNZydxoVrwSlEKVfCMrIjsha2HpSCFSlmseCMekAWlN9q9EMWKoNB6QHHizcP3_nzvx8fP-537RYz0HcEj-8_9PvXHzrEHvkeI1Z4QPkf4et3WDiFEg13tjtWy93p6KnUin7ZX3bQ16O3NZXLF9CFPu85yN105OpctpBdKVtpaWgqLUc8pRjz_jjc8-NY8SHs8jJXF_xxOfn6ItaEm6_O6V73ioaFPSBN9Z6lnOVbnNsde6S13V9oDW57N1edzuVKzUFtoWtZ8bq5YLxXtUq1uFbJ2MZ9tFoqFYqlWyCjeiAvC17D7Yvx4rbrSbtjVbD6TWS1ksmJnM9-yFjvipuH-7L4TbZvJM0SOEHmZyHlUGfVfohWizxJ9h-gFzGNor6G_i34R_SviV4hfxwBDwjiO8SvJv0i9QKqOuAfzAP4QQYfg64TWCUcIF5l-iun3mfkUrYtWQ7-dxJckD5C8gVAROcSDyB-hTDC5QSRPtImmoM2S8JEwSVwhuYF_FP_bSHnMe5G7KD2UdcxDqA3Uz1B_IxEmMU9ijcTnJAsE9hO4TmSd0CWkt5D3IVeRLeTLyF-g3IfiMnkadRPtMNqTaJeZvZXYNrEbxP4m9g_6GPo4-m70M5gPE_8ZI4rxEoaLcYnEUW7ZIKmQVEl-R-hNQucJ_US4y_iHRE8SXmB6wPSrqOtELxLdQmsQ2yT2McYmQYXwtyhXMfcQeYbIJlNb6KeIXyVZJfkJYhTxBObd7NrGfxj_CQI-Ao8ROElgm2AQ8yDB9widJrSFFEJ6FKmH9BzhCuYHhJ9GfZGZHtpZtK_R96H3iP-JMYt8B0oI1fu6U5g3Y_xIcAbpGuFryCPIryD_QOQbL0Qtuztoe-nu2F23fMTtN9rLqcfbDXexnM-UCqlFu91adMtzmWIuZS31Fq2y6_TtVN3q2I5Vrhy7P3dXtVKdq2YymZTV9a7IbXtRLqc6tms1LNca2M6K91LOTfi85v8AtYt2u40DAAA.png","cards/q4-sportback-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TW4gbdRTG__3F7W6TTLIzy2Z3smMimUzYjsZOLs02lYApKlQQe7HFSyFONpNNyiabzk7iQrXgk6IUquAd2SKyD7VeloIUVmSx4otYRApKX2z3QRQrgkLrBcWJLx_nO3zfOX_-fOf8L2Kk7wqe2Hf-96k_to89cg0hVnpCBFwR6HUXtgkhGuxod-wFZ5fPpzInillnxcvag96uvJWfyx70uecudbPVI4VcKbunbGftxcWoGPWdYsT3b3vbh8CqD5G7fBiriP9xOPmlIawOObmAr17xi8eGPhGZ6LuLPdu1O3e7znJvqbvcHjjyrFVv5OatcrO-2yk27flSs9Ao5EtWsZmzmn6nXC_bu0u-SPFHXBSBhtMX48frteV2w6nlipa1UrJyYnuz6Nmtjrht-H52nkPbYvIMscPEXiN2AVVG_Zd4lfgLxM8Rv4h5FO1Nku-T3CD5NamrpG6igx5BP47-K8ZfZF4mM494AHM_QYmwS_gtpDWiMaJzTD_L9IfMfIHWRauTvIf0ZYz9GLcQKiKPeBT5E5QJJteJFYk30RS0WdIB0ibpqxjrBEcJvkukiPkQchelh7KGeRC1gfol6m-ko6SLpFdJf4VRIrSP0E1ia0gbRN5B3otcQ7aRLyFfRnkYxWPyNOom2iG0Z9AuMXsniS0St0j8TeIfkmMkx0neQfIM5uOkfkaPo7-K7qF_SvoIO9cxFAwV43uks0gXkH4i2mX8Y-Inie5hesD0G6hrxDeIX0FrkNgk8Rn6JmGF6Hco1zEPEHue2CZT_qJTpK5j1DA-R4winsa8nx1bBA8RPEEoQOhJQicJbREOYz5I-AOk00hXiEhEjhHpEXmRaBXzI6LPob7CTA_tPbRvSO4l2SP1J_os8r0oEqr_dacwb0f_kfAMkRtEbyCPIL-O_AOxb_0QLTjdQdtPd8fpepXDXr_RXso81W54rUrRKpcyLae90PIqBWsun7EXey274rl9JzNvdxzXrlSPHsjfV6vWCjXLsjJ2178ir-1HuZLpOJ7dsD174LjLfqeSnwj44v8AQPe5so0DAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q4</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:21.136Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q4</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q5-suv.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSk_IztUhB2olJGHYTn3jH02vseip-3cZHh4ynHf3yc3_GdgBZrDOB1IMJ8FEvwMQIJjPYQE2VADIiaC-EyGzAwMrBVARiQDCPDxlRblFCQWJebqpaQmlaYLahgQCYTZXVxDHD19ggHJwayh4wAAAA","cards/q5-suv-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_yWTS2wbVRSGbz6TpHVmPJmJ4tjTwUaeGRMFmY4fcdpSIxy1WbCgRGmCKiTciT1xHGLH-BFS0gUbBBsqkBChIMSCsoGICirxKgKlPASCCokiUcGmsAIRxALUUBCIidh8OufqP7907_3P5q-it9sS3D-5-fvIn317jl9DiLWmEIEzItBsVHuEEBX21upu1dvv9yO3PjSe8tY6KXe1uT_jZCZS0-Ope6ZSM7NzqeJsLruWmjpRTLnLy4ro90dFr2_Qs-EjcNmHInzsOf8_d61P7-Lp3Z50wFev-cWJ3TkRGuq2lptuy63f3vLazZVGu7bqqaP5ygGnkk3ny-O58Vw67XgL5cxCZSGbdfIH8wfKnpNbyORzE47mW2yJQMXrisGl-VK7VvFK6ZzjrOWdtOirdufd9Clx0-4FSIxwc5nhpwjPEL5A5C-ih9HH0Ivoz6C_iv4OxlniKeKvEL9I_AqJqyT-wOzBXML8DftfkkdIthF3EZSRWihhIutEzrPvU4wGxjzGk4zViN-BtYH1FfYOIoP6PtoQw88RniB8FL2KoWGMYgWwxrC-w36DYD_Bc0h3EsqhrqM9gPYJ4RjRB4l-QfQ6-jaWgpXAegnrc-wsA5MMXEd6F22K8MvIryNfQn4L-QbqIdQSqov6Eeo3aKNo42jH0LpEL2JMYzzC6G3Evie2Q-xvYv8Q7yU-SOIzEr9g6pjPYnYwP8Caw9rB1rAt7Luxj2FfQzqHvIF8AflnlAbKCwzOMlhD91-jTeR5xk4S3US_D_1t9PcwysS2iF3C_BBJQ7nK8GGGFwk_QXiLkaNElog8hl3CPov9sR9ORD_iNHu3CU4SnCFYJ_glAycZWGfgRyQJ6U3kM8hXCMmEDEKPohRRjqM8TvRF9B_Y18R4DeNr4oeIzxFfJXEDcxR1Ck0mOk30FIaEeRnzJ6Q-pFsIbaNso_ai-p-1TvhbP19Vr7Faa6006l6jU5jpdCu1leTDtUpnsZBzDuaTi16tutgpZJ2JTNJdbi66hU6r6yXLbt1ruYXi3L2ZI6ViKVtyHCfpNvwN69T8lBeSda_jVtyOu-q12v5JITMU8MX_AfxvcgapAwAA.png","cards/q5-sportback.png":"https://mediaservice.audi.com/media/fast/v3_yWTTWwbZRCGvz5umtbZ9WY3ZGNvF7vy7lpWKtO1Y8dNwYhEJUgcKCVNUcXB3diL4zR2jGOH0PTABcGlCETFTxGiKnApFRUUVYhWghaEKlA5UCQqQIJy4ieIA9DwIxAbcXn0zWjemdHo_U7_LHq6bcEDE6d_Hfpj0-Z93yLEckuI0FERajVrG4QQVbbUG17N3xHEQ6mHChl_uZPxllo7cm6umNlbyNwzmZmayIxP50eWM5MHpjLe_LwiegOl6An0G54LELoSQBEBNp_5n-udj6zj6fWYbCioXg4eB9Z1IjLQbc-3vLbXuKXtL7YWmov1JV9N5_0Hi5W8P1oszIz5lRE3vzM75ud8rzoyWsxWKoWdleqYW8jntKDFRRGq-l3RPzdTXqxX_XI277rLo25WbKp1m97hmti4vj_bTnHzdQafQp9CP0v0R2K3YQxjjGMcwziF8Q7mcRIZEq-ROE_iKslrJH_HElhzWL_g_EtqN6lDiDsIy0htFJ3oCtEzbP0Is4k5g3mU4TqJW7Gfwf4UZw2RQ72ANsDgMfQiejCuhqlhprFD2MPYX-K8SbiX8KtItxPJox5GW0C7hL6d2CFinxD7DWMVW8FOYr-M_TFOlr4J-m4gvY02if4K8hvIl5HPId9A3YVaRvVQP0D9HC2NVkDbg9Yldh5zL-YK6e3EvyK-Rvxv4v-Q2Eiin-Rlkj9hGVjPYnWwLmBPY6_haDg2zt04e3C-QTqJfAL5LPIPKE2UF-mfpv8vjOAai0SPM3yQ2EmM-zHOYbyLWSH-PvFLWO8haSjXuCnN4Cz6E-gXGbqT6BzRx3DKOC_gfBh4E9GLOMKWVcJ3EZ4i3CD8NX0H6Vuh7zskCekt5CeRrxKRiZhEHkUZR9mH8jixlzCus7WF-TrmZyR2kdhPYonkn1hp1Ek0mdh9xB7BlLCuYH2PFELaRmQVZRW1B_V59BX0LwJ_1fzmUr290Gz4zU5pqtOt1hdSD9erndlS3h0bTc369dpspzTiFnMpb74165U67a6fqngNv-2Vxvffm9tdHi-PlF3XTXnN4IN16oHLS6mG3_GqXsdb8tuLQaaUGwgFxf8BX3a0S6gDAAA.png","cards/q5-sportback-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_yWTW2gcZRTHv_zWJO3uzE5mYja703FXdmaWEFm7t2Tb6ooJNUIfrCFtpAhuJ7uTzcTsZt1LTEkffBF9qSiItYooWF80WLTgraLEGxWtD1aw6Ev1yUvEB6WxiOIsvvz4zuH8D4dz_t_mb6K_2xLcP735x-hfA7uOXEWI9aYQgVMi0GzU-oQQVXZ7dafm7vXj0dRDE2l3vZN21pp7c5lcMT07kb5nJj03nZ46Wsivp2eOzaWdlRVFDPpK0e_r-077CFzyoQgfu879z17nkz081YvJBvzqdf9xrKcT4eFua6XptJz6rS233VxttL01Vx0rLFYXJp3FrFvJ5PY72Yl9i8XJhVy-kHedfflKPlvN57LFiaKj-S22RKDqdsXQ8kK57VXdcraQyaxPZrJioNZtONkT4obe_CRHuanCyJNE5oicJ_oLsdvRx9Gn0J9GfxX9HYwzJNIkXiFxgcRlkldI_onZh7mM-Tv2v6QOkmoj7iQoI7VQIkQ3iJ5jz2cYDYwFjFOMeyRuwzqN9RX2DiKH-j7aMCPPEikSuQu9hqFhjGEFsMaxvsN-g-AgwbNIdxAuoG6gPYD2KZE4sQeJfUHsGvo2loKVxHoR63PsPKFpQteQ3kWbIfIy8uvIF5HfQr6OegC1jOqgfoz6DdoY2gTaYbQusQsYsxgbjN1C_HviO8T_Jv4PiX4SQyQvkvwVU8d8BrOD-QHWPNYOtoZtYR_CPox9Feks8kvI55F_RmmgPM_QUYY8dH8bbaLPMX6c2Cb6fehvo7-HUSG-RfwjzA-RNJQr3HiIkSUijxPZYtQjukz0Uewy9hnsT3xvIgYRJ9m9TfBugnME6wS_JHSc0AahH5EkpDeRn0C-TFgmbBB-BGUK5QjKY8ReQP-BPU2M1zC-JnGAxDyJNZLXMcdQZ9BkYrPETmBImJcwf0IaQLqZ8DbKNmo_qn-sDSLf-v6quY01r7XaqLuNTmmu0616q6mHvWpnqVTI7J9MLblebalTymeKuZSz0lxySp1W101VnLrbckpT8_fmDpanyvlyJpNJOQ3_g3U83-WlVN3tOFWn46y5rbafKeWGA37xf7LnYnmoAwAA.png","cards/sq5-suv.png":"https://mediaservice.audi.com/media/fast/v3_yWTXWhbZRjH3_6yrltyktNzQtPk7JiMnJxYKrEnSZOu0wgds4gXztm1ZXoRT3tO02xNGvNRqx3ijTAvHArqrOJd2cWcbmyi4gZSB34gRdwuHIJQvVKoeiG2fiB4ijc_nufl__xf3pf_c-kX0d1pCp44cun3_j_37juxiRDLDSF854SvUa90CSEc9ldrdsUd8vr-u58qZNzldsZeagzlrNxI5ngh88h4ZmJyKjM2OZxfzoyfHMvYCwuy6PFGRbdn0HXeg2_Dgyw87Lv8P3etz-zild2erM9TL3vFyd05EQp3mgsNu2nX7m26rcZivVVdcpWBnGMdsnNFuzhXcEbyc4VDswUnOzw6ky9m50bnnGxxLp-3itlZ1bNYFz7H7YjeUzPlVtVxy9lhy1ouWlmxt9KZaRWeEXt2H8DB09y1Qt_LRCaIXCP6N7H70QbRjqC9inYR7SP0VRJDJC6SuE7iNsk7JP_A6MKYxviNdJj0UdI2ooQ_iNREjhBdIXqZA5-h19Fn0F9isEriPlLnSX2NuYMooNxADdP3GpE8Ee-6CrqKrpPykRok9R3mFfw9-NeQHiA0jPIs6uOon9N3i9hpYl8R20bbIiWTSpJaI_UlZp7AQwS2kd5HHSdygeB7BD8l-AHBbZTDKGUUG-UmyjeoA6gF1GOoHWLX0Y-jrzBwD_Hvie8Q_4f4vyT2kOgl-QXJXzE0jNcx2hg3SE1hgqlixjAfxjyGuYm0RnCV4DWCPyPXkd-id5LeHTTvN1pE32TwSWLvok2jfYj2MbpDfJ34TYxPkFTkO4RfpG-eyFki6_RXiZ4i-gJmGXMVc8MLJ6IHcYb9W_gfxD-Bv4Z_k8AMgRUCPyJJSFcJniN4m1CAkE7oeeQx5BPIZ4m9jfYDBxro76DfInGYxDSJJZJ_YQygjKPKxB4j9hy6hLGB8ROSD-kgoS3kLZRulDeIrBD51stXxa0vVZuL9Zpbb5cm2h2nuph-uuq050vD1mgxPe9WK_PtUt4ayaXthca8XWo3O2561q65Tbs0NvVo7mh5rJwvW5aVtuvehrWrXspL6Zrbth27bS-5zZZ3UsqFfZ74P_uXrwupAwAA.png","cards/sq5-sportback.png":"https://mediaservice.audi.com/media/fast/v3_yWTX2hbdRTHf_1kXbfkJrf31qbJ3TVXcnNDqcSm-bPYaYSWWWQPzpltZfoQb5LbNLNJY_4Z7RBfhL1MFNRZxbeyhzmdOFFxAykDnUgFtweHIFSf_FP1QWwVEbzFlw-_czjfcw6H7-_Sr2Kw2xI8Pnvpj7G_9u47vokQ_aYQnnPC02xUB4QQFfbX6nbVmXTjsfhT2YTT7yTsXnMylUzlEseyiYfnEoXZxMyJTLqfmDtVSNhLS7IYcpVi0NUPnHfh2XAhCxf7Lv_P3c5ndvHybsyUx63uu49TuzoRGOm2lpp2y67f03LazeVGu9ZzlPGFbKnsZMs5u5Ipl51MyklNJ530wr3TCxUnlyulc7ZTmSrlFlS3xbrwVJyuGD5dKrZrFac4lUkm-weTU2JvtdtoZ58Re3b3x_iFO1cYfYlggeAVQj8Tvh9tAm0W7RW0i2gfo69iTGJcxLiKcYvobaJ_Yg5gzmP-TnyE-GHiNiKP14_UQg4SWiF0mQOfoTfQS-jnmKhh3EfsPLGvsHYQWZRrqCOMvkowTdAdV0VX0XViHmITxL7Feg_vEN41pAcIZFCeRX0M9XNGbxJ-kvCXhLfRtojJxKLE1oh9gZXG9xC-baQPUOcIXsD_Lv4b-D_Ev41yCKWIYqNcR_kadRw1i3oUtUv4Kvox9BXG7ybyHZEdIv8Q-RdjD8Yw0RtEf8PUMF_D7GBeI3YSCywVK4x1BOso1ibSGv5V_Ffw_4TcQH6T4RMM76C512gTeoOJJwi_gzaP9hHaJ-gVIutErmN-iqQi3-aOI4wuEjxLcJ2xGqHThF7AKmKtYm243kQMIc6wfwvvg3gLeOt4N_GV8K3g-wFJQnof_4v4bxHwEdAJPI88g3wc-Szht9C-50AT_W30mxiHMOYxekT_xhxHmUOVCT9K-Dl0CXMD80ckD9JdBLaQt1AGUV4nuELwG9dfVafRq7WWG3Wn0ckXOt1KbTn-dK3SWcxnktMH44tOrbrYyaeTuVTcXmou2vlOq-vEy3bdadn5mZOPpA4XZ4rpYjKZjNsN94N1aq7L8_G607ErdsfuOa22m8mnRjxu8X_ZIgjzqAMAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q5</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:25.980Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q5</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q6.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q6-suv-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbZRzHn32ytV1ySXpXd81lZzJyd7FW4i5Z_qyTiJlSRcQpdRPxRXZpLmlqk2bJpXbUF74ZE2GgKDIEmXT6RosiA5Epbk6RoSDi3mjxxTpRJlYEhU0RxatvPjzfH7_v73l-8H3WfhU7Bj3BkwfX_hj_c2jksasIsdwVInBSBLqd5jYhRJ2drbbTdPf6ejztFDPuspdxlrp7c3aulDnma6-32MlUDuezy5lGoZ9xFhaiYth3ih2-f9uQj8CGj8hbPkZ-Ev9za_LxLTy_pbEDfveyf3hiyyciY4PeQtfpOe07e26_u9jpt5ZceaLounat6GYbDddxC7PZUqM-lSvUCo1sPZfN5gu1UqHg5PY3FH_EBRGouwMxOl-r9lt1t5rN2_Zy0c6KoWaj5mQdsX3r_ey5l1s32PUC6gzqObQQ2r_EK8RfJL5G_AP00yQzJN8k-SHJK6TWSd3AACOIMY_xG-kk6YcQ9xAMEAwTPIHUQzpDVCW2Quxddn-O3kGvoZ9iskXyLsyXML_GegDrJiKH_BHKGLteRi2h-lc30RX0CcwA5iTmOtZ7BIcJvoF0G1IR6W4ieZQ2ynnUANpTaF-i_Y4ZxUxhVjHPYH6BlSd0kNAN5E2UGMo06lnC7xC-RPh95APIVWQH-VPkr1AOoQzQLqI_jL7CxB0k1kncJPE3iX9IjpAcJXWZ1C8YcYxXMDyMjzEPY17HUrA0rAexDmFdRVol_Drhc4R_Jtph9BjGFLE-sVeZPIq2Svxx4ufR6yQukrhE4keMC0gK0W-5ZRb1OdRPGB8jNk_sBFYV6zPEMOIZdl4jeD_BGYJtgt8TOkpohdA1JAlpP5K_2inCV4iEiehEniVaIXqE6Eluv4w6jfYa8Q12d9HfRv-G5AFSf2FMIE-jhNEeRTuOLmFcRxpC2kNkk-gm8nbk08iryD-gfucnq-l2llp-5NtuxyvPeIN6azH9dKvuzZXz9lQxPee2mnNeeZ9dyqWdhe6cU_Z6Azc967TdnlOuHHkkd1-1Ut1XtW077XT8r-W1_HyX023Xc-qO5yy5vb5fKefGAn7zf7KBWguiAwAA.png","cards/q6-sportback-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbZRjGv_2ytV1ykvScstOc7JhozjmxrcTlX5N2ErFDOpHhlLqJeJGdNqdpapJmyUnNqBfeDGUwUBQZgkyq3miZyEBkipt_kKEwxN1o8WKdKBMrgsKmiMMTb368z8f7Ph8vPO_Gb2JXty146sDGn6N_DQw9fg0hei0hfKeEr9Ws7hBCVNhda9hVZ5-nR8ftQsrpuSl7tbUvm84WU8c97bZXmqnOfGrmSD7TSy1OtlN2vR4Wg96w2OVZ7Bjw4NvyEHrHw9DP4n_2zU_0caqvSfu87p5XPNmfE6GRbrvestt2496202mtNDu1VUcem59czBbydnbBcSoLmalCPlfJLGYq085ULmdP54tT88VMcTI7qXgWF4Wv4nTF8PJ8uVOrOOVMPp3uFdIZMVBdbNoZW-zsr8Bdh7hjiz0vos6hnkcLoN0mOkP0JaIbRD9EP0M8Rfxt4h8Rv0pik8RNDDD8GMsYv5OMkzyEeAC_D38Q_0mkNtJZwiqRNSLvsfdL9Cb6PPppJmrE78N8GfMK1kNYtxBZ5I9RRtjzCmoR1fu6iq6gj2H6MCcwN7Hexz-I_y2ku5EKSPcTyqPUUS6g-tCeRvsa7Q_MMGYCs4x5FvMrrDyBAwRuIm-jRFBmUd8keI7gNwQ_QN6PXEa2kT9HvoJyGKWLdgn9EfQ1xu4htknsFrF_iP1LfIj4MInLJH7FiGK8iuFifIJ5BPMGloKlYT2MdRjrGtI6wTcInif4C-Emw8cxpol0iLzGxDG0daJPEL2AXiF2idhnxH7CuIikEP6O8duoL6B-yugIkWUiJ7HKWF8gBhHPsvs6_oP45_A38P9A4BiBNQLXkSSkKSRvtdMErxIKEtIJPUd4hvBRws8zfhl1Fu11olvsbaG_i_4t8f0k_sYYQ55FCaI9hnYCXcK4gTSAdCehbcLbyDuRzyCvI_-I-r2XrKrTXK15qW84Tbc053YrtZXkM7WKu1TKp6cLySWnVl1yS7l0MZu0660lu-S2u05ywW44bbs0c_TR7IPlmXKunE6nk3bTuy635uW7lGw4rl2xXXvVaXe8l1J2xOc1_wez14KNpQMAAA.png","cards/sq6-suv-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbZRjGv_6ytV1ykvScrmlOdkw055xYK7Enf5o2k4gdWoaIU6od4kU8aU7TzCaNyUkXqYg3wyEM9GZMQQQpXtTiFEVExVVHZSgizhvt1TZRFKqCwqaI4qk3P97n431e3g-ed_MXsb_bFjx2ZPOP0T_7Bx--ghC9lhC-54Sv1az1CSGqHKg37Joz4enRlF1IOz03ba-2JrJWdir9pKfd9kozPfNIPtNLL0520vbyclgMeE6x3_P39XvwXfUQ2vAw-KP4n3uTn9rD83say-d197zi0T2fCA1328stu2037mg7ndZKs1NfdeQxK5urLtiVXNGerDjV4kIhk5vMFAtOLm8VnEUnX3Wmi1OLmYLijbggfFWnK4ZOVMqdetUpZ_KW1StYGdFfW6x0JqfFvr39ueV-blpj5AUic0TeQQ2g_kvsCLEXiW0Sex_tHIkJEhskPiRxmeQOyevofegH0Y-j_0YqSWoeUcLvwx_EfwqpjfQq4QjRNaLnOfQZWhOtgnaG8TqJOzHOYnyFeRTzBmIS-SOUYUbOE8kRuZtYDU1BG8PwYYxj7GC-hX8A_zrSrUgFpLsI5VGaKNuMbKM-gfoF6u8YYYwkRhljHeNzzDyBowSuI--iRFFmibxO8E2CnxJ8D_kwchnZRr6I_DXKMZSTqFtoD6CtMXY78R3iN4j_TfwfEoMkhkheIvkregz9LLqL_jHGPCaYCqaKeR_mMcwrSOsEXyL4LsGfCTcZ2kIvEu0QfZnxx1E3iB0n9gFalfgW8YvEf0C_gCQT_paDbxM5TeQTRoeJniB6CrOM-SViAPE0B67hvxf_HP4G_m0CFQJrBK4hSUjTSN7XzhD8hlCQkEboWcIzhOcJn-a2S0RmUV8hdpVDLbQ30C6TOEzyL_Qx5FmUMOpDqM-gSeg_IfUj3Uxol_Au8j7kc8ivIX9P5DsvWTWnuVr3It9wmm5pzu1W6yupk_Wqu1TKW8VCasmp15bcUs6ayqbs5daSXXLbXSe1YDectl2amX8we095ppwrW5aVspveabl1L9-lVMNx7art2qtOu-O9lLLDPq_5P8A7voSiAwAA.png","cards/sq6-sportback-e-tron.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoRk_IztUhB2olJGHgf1-2Ym9s_xSY4TqV96PP37HcbYJHwMr0BxGNiDB_BBI8K0CEhzPGMAkyIYZIGI-iM-kz8zAwFoBZEQygAAfX2lRTkFiUWKuXkpqUmm6oIYBkUCY3cU1xNHTJxgAWgcLIuMAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q6</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:30.533Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q6</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q7.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q7-suv.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoTk_IztUhB2olJGH4Wdzv6Sh50eFh52zTiU5L5xc0nYhn4EVaA6jOJBgjgASfEeABEcnA5gE2ZABIvJBfCZjZgYG1gogI5IBBPj4SotyChKLEnP1UlKTStMFNQyIBMLsLq4hjp4-wQBRTCXI4wAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q7</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:35.520Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q7</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q8.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q8-suv.png":"https://mediaservice.audi.com/media/fast/v3_x2TT2gcdRiGf3m2SdvNzG5m4k53N0MGd2a2IZJmdpPmn11pahERtNLWFvGwmWRnk02zk83ubJraKnoQvFQvxaJCe1AiaBWCImKLtBYaghiqHpSe1IuK6cWiNeSgk14evhfe7-U9fN-Vu6K1WRe8cOjKvT3_tu06_jNCLNWEiKyISM2fbhFClNhdqbrTXn-o9-gLI33eUtDnLtb6805-uG9hpOb2DVbLfe7cXFzsDP2iNdxqORAicj1E7EaIXSviAR_kbePctiYXCd1L4fD89p6IdTbrczW37lb31b1Gbd5vVBY9pWfUy40MDU9NjXiT3vDkaHl_bsDxyrncaFggP-KW97vuwECp7KhhxJqIlLym6JidLDYqJa-YG3ScpSEnJ9oGq4EzmRc7tlvz8Brd_WjH0D4lZZM6QLqX9DjpC6Q_JP0FRj_GMsZVjHWM78jcJvM35gTmX2RlsofJ-oiDSHXkZeIaiSbJl-m6he6jT6Cfp7dC5g-sd7DWse8j9hF9FOVNlGuonSQuoA2TnkXvRN-L_iRWBKsX6w52Avsk9grRVqLvI-1FGkJ6DDkgNojyNMqLqPOoqyS2SL5Hyif1Dan7pDcw2zA3seJYJlYR6zLW19iP0_4U7f8gfYb6BNoy8m3kz5HvIm-hjKEUUVyUmyjrqD2oBdQjqM-hNkmcJ7WK_gz6l_Q8QvcdurcwdmB0YNhk_sR8CzPAvIZ5A_MW1gms_7BV7BT2EewNpA-QLyL_Rtwn_i4dx-m4h5nHHCXZJH0VSSH-Ew9tkphBex3tOskxkrMkX8M4hV3GXsB-G3sN0YLYiTjH7g2ih4geJVolukr7JO1naf8VSUb6COkT5AnkN5B_ICYT04m9Qnyc-KvEL9PRQ-oS6V_oqqF_jP493V9hjGGcxFgks4nZg3KQ1FFSZ9AlzG8xf0dqQ-oitkF8A6UV5SLaWbRLaDfRfgzv7iXPX6zU5_2q5weFY0GzVJnPnq6UgpnCoDM6lJ3xKtMzQWHAGc5n3bnajFsI6k0vO-VWvbpbGD_xbP5wcbw4UHQcJ-v64bsFlfD6C9nG1HwtdJw-5Z1peAtNz5_yCvls1Qvckhu4i169EfoK-c5IGPE_puUsMswDAAA.png","cards/q8-suv-e-hybrid.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbdRjHb5_Ybkvvkt7VpEl69CB3l5VK1-s1bdK6yKoyRNCpcxvDF-ml-aVN16Rpcmk7OkFfCL6ZL2Q4ZLC9UCqMKRRBhcnoVDaGWIZ7oeyV-maK3Rv_bcMXet2bD88D3--X58X3uXxP6mg3JV57-vKfvQ8697z6E5K02pCk0IYUatRnd0mSVGZvtebNiuFg79WX8kNi1R_ylhvDruPmhpbyDW8oW6sMeQsLUWl3oJc6AteuAwFCmwEi1wLs2ZAe8VHeDk7v7IyEAvVqMJzY8UmRnnZzoeE1vdr-pmg1Fuut6rJQB2by5bxbEaO50ojrOjPjeafk5vKjlTG3MjExInKlMSEqjshrQcRNKVQWbal7vlRsVcuiOJJ1nNVxZ0TqzNZ8xx2VHtu5mnQv_cPEjxD_lKRN8gCpQVJTpM6SukTqC4xhjHWMKxhbGLdJ3yL9F-Y05h9kFDLjZCpIB5GbKOtE48TaJNbou45eR59GP8NglfRvWOextrDvI-0n_CTqu6hfovUQO0s8R2oevQd9H_pzWCGsQaw72DHs49gbhDsIf4i8D3kc-SkUn0gW9QXUNbQTaJvE7pL4gGSd5Lck75PaxuzEfIgVxTKxilgXsb7CztL1PF3_IH-Odoj4OsotlM9Q7qH8jTqJWkT1UL9G3UIbQBtDO4x2FK1N7AzJG-gvom8y8AT9d-j_F6MDoxvDJv075nuYPuZVzGuY17GOYf2HrWEnsQ9jbyN_hHIO5S7ROtHzdB-lewXTxZwg0SZ1BVkl-iOPPyA2R_xt4pskJknMk3gL4yR2BXsJ-33sm0E1kXYjnWbvNuFnCL9CuEb4Bl0lutbo-gVZQb6E_AnKNMo7KLeJKER0Im8QnSL6JtGLdA-QvEDqZ_oa6B-jf0__VYxJjOMYy6QfYg6gHiT5MslT6DLmd5i_IoeQ-4hsE91G7UA9R3yN-AXi3xD_Iejd66K-XG0u1mui7heO-O1ydTGzUi37c4WsMzGemRPV2Tm_MOrk3Iy30JjzCn6zLTIzXk00vcLUsZfcZ4tTxdGi4zgZrx68m18N2l_ItGYWG4Fi5aQ41RJLbVGfEQU3UxO-V_Z8b1k0W4Gu4PaEgoj_ARtX15fMAwAA.png","cards/sq8-suv.png":"https://mediaservice.audi.com/media/fast/v3_x2TUWwTdRzHj0_ZgPau3d3So-2OndndlWU6d-26rkNqGKjhBTEgoPGhXNf_to6169prNzMkRmPiCyYaoyEk-iCZiaKRaIwRYkANhhAJ6oOGJ_VJ4vABE5HwoDdePvn9ku_3m9_D93f2ltTVbko8t_vs31v_7d789K9I0nJDkkLnpFCjPrNBkqQKW6o1b0aMBPtWY7EwLJb9Ya_TGMm62fHhxULDG87Vpoe9-fmYtCnQS12Ba8POAKGLAaKXAmw-J93n_bx1HF_fyYQC9XIwPLvuk6K97eZ8w2t6tYebotVYqLeqHaEO5kXec8u50XJBTHliouCWhRBj47lRbzpTyJTzucKE501lhRZEXJFCFdGWeubKpVa1IkqZnOsu592M1J2r-a2ljLRx_WoeMNm2C_0g-qckHZI7SQ2RKpJ6k9QHpL7AHMFcxTyPeQ3zBwauM3Ab6wjWbdIJ0ntI70PajdxEWSWmE2-TWKHvMkYd4yjGSYaqDNzEfhn7Gs4dpDHCj6C-gXoBTSV-Gn2U1BxGL8Z2jL3YIewh7Bs4cZwjOJ8Q7iJ8Bnk7ch75URSfaA51H2oHbQHtKvE_SbxHsk7yKsk7pNawurHuYsewLewy9hnsr3H2ENlL5B_kz9CeQF9FuY7yOcotlHuoO1BLqB7qN6jX0AbRxtD2ox1CaxM_SfI7jCcxvmTwQfpv0H8PcyNmD6bDwF9Yb2H5WBewLmFdxj6M_R-OhpPE2Y-zhvw-yimUm8TqxE7Tc4ieE1gPYU2QaJM6j6wR-4XeEPFZ9FfRL5LYRmKOxCuYx3CmcRZxTuFcCaqJtAnpOFvWCD9O-ADhGhGFSJnICpHfkRXkD5E_RjmK8hrKT0QVogbRF4lNEnuJ2Lv0DJJ8ndRv9DUwPsL4kf6vMHdgPoPZYeAu1iDqLpIHSJ7AkLG-x_oDOYTcR3SN2BpqF-rb6Cvo76B_i_5z0LsXRL1TbS7Ua6LuFw_67Up1Ib1UrfizxZw7kU_PiurMrF8cdcezaW--MesV_WZbpKe8mmh6xcnDT2UfK02WRkuu66a9evBufjVofzHdmlpoBIqlY-L5llhsi_qUKGbTNeF7Fc_3OqLZCnTFbG8oiPgfYJgXjcwDAAA.png","cards/rs-q8-suv.png":"https://mediaservice.audi.com/media/fast/v3_x2TX2hbZRjGv_2yrl1yTpJzStImPfRIz5-VltokTdN0LrJKkQn-KdvcFMF41py22ZrTNDnJqt1AFEGQeSGiE0EZjA10igMVcUOs4KQMy9QLRRTUK8XOC8XNsRtPd_PjfeF5H77ve5_vwnXR0WoInrjvwj89_-3oOvgLQqzUhQhdFKG6N79NCFFhZ7XmzLujQd-jLRdH3BV_xGnXR3OZ3MTIcrHujORrcyPO4mJMdAZ60RFMbdsTIPR5gOhagK6L4g7v-G3hxFZPNhSoV4Li8a05Ee1uNRbrTsOp3d1wm_Ulr1ltu8rg3KQz5uSdfHa2MlfMzY2PFbLFidlsYWKymC9WssXCuFMYcxxXDSzWRajitkT86JFys1pxy9l8JrNSyGTFjnzNb7RzYvvWqbnrJP06yQMkPyJlkdpDeoj0vaRfJf0O6U_QR9HPo19C30D_hoFrDPyLcRjjb-we7GnsGcQDSA3kc8SSJFr0rtJ3Bc1DewrtFENVBv7AfB5zA-smIk_4HpRXUC6jKiROk8yRrqN1o-1C24cZwhzC_BErgXUY6wPCHYTPIg0jFZD2IvtE8ygPoTyDWkf9msSf9J4h5ZG6Suom6U2MHRi3MOOYNuYRzLOY61jTRPYRuYH0Ier9JM8hX0P-GPk68m2U3ShllArKlygbqIOo46iPoB5EbZE4ReortIfRPmVwmP6f6b-Nvh09jm4x8BfGaxg-xmWMNYwrmIcwb2CpWLuwZrB-RzqPfBr5J2IesTeJP0r8DMYwxiS9LdKXkFRiP9D9JIkFki-SXKOni96j9L6AfgxrDmsZ6w2s9SCaiE7ECXZuEn6Q8H7CNSJRIh6RVSK_IclI7yK9j-wgv4z8HVGZqEb0WWJTxJ4j9jbxQVLBln-lL3j899C-pf8z9N3oj6G3GbiFMYiyl9R-Ui-hdWBcxQhuEULqI7pJbBOlE-V1kqsk3yL5Bcnvg9yddL12tbHk1VzPLx3wW5Xqkn28WvEXSvnMZMFecKvzC35pLDORs53F-oJT8hst1551am7DKU0dmslNl6fKY-VMJmM7XvDd_GqQ_pLdnF2qB4rjx9ynm-5yy_Vm3VLOrrm-U3F8p-02moGulOsOBRb_Az2lI7rMAwAA.png","cards/rs-q8-suv-performance.png":"https://mediaservice.audi.com/media/fast/v3_x2Tb2gbdRjHb5-sXZfcJbkruTbp2YPcn5WW2iS7_slcxEqRvZg6ttkpvojX5Npma65pcumqnSCKIMh8IaITQRHGBjrFgYq4KVZwUgal6gvFP6C-Uux8obg5huB1bz48D3yfL7_f7_n-LlwTOtpNgUfvvfB3z7-dXUd_RhBWGoIQuShEGv7cDkEQquyu1d05byTse7SliWFvJRh2lxsjhVxhfHhpouEOO_XZYXdhISHsCvVCRzi1Y3-IyGch4mshui4Kt3nbbxuntnvykVC9EhaPbM8J8e52c6HhNt36nU2v1Vj0W7VlTx5wipXiWLHgOBMzRbc67nrObHGmmHPcyqhbqE4UnXx-YnzUySuhxboQqXptIXl8ptyqVb1y3snlVsZyeaHTqQfNZkHYuX1qshp3_IB6BPUD0hbp_WQGydxN5iUyb5H5CH0E_Tz6JfQN9K_IbpL9B-MYxl_YMvYUdgXhIGIT6RwJlVSb3lX6rqD5aI-hnWawRvZ3zGcwN7BuIDhE70J-EfkyikzqDGqBTAOtG20P2gHMCOYg5vdYKaxjWO8R7SB6FnEIcQxxCikg7iDfj_wEyiLKVVJ_0PsmaZ_0VdI3yGxhdGLcxExi2pgzmGcx17GmiB0gdh3xfZT7UM8hbSJ9iHQN6RbyPuQychX5C-QNlAGUUZQHUY6itEmdJv0l2gNoHzMwRP9P9N9C34meRLfI_onxMkaAcRljDeMK5jTmdSwFaw_WIazfEM8jnUH6kYRP4jWSD5H8BGMIo0hvm8wlRIXEd3RPk5pHfQ51jZ4ueo_T-yz6CaxZrCWsV7HWw2gi7EI4xe4togeJHiZaJxYn5hNbJfYrooT4NuK7SC7SC0jfEJeIa8SfIjFJ4mkSb5AcIB1u-Rf6wsd_B-1r-j9F34f-MPoy2ZsYA8j3kD5M-nm0DoxNjPAWEcQ-4lsktkj-h_wK6irq66ifo34b5u5Jz1-uNRf9uucHpSNBu1pbtE_WqsF8yckVx-x5rzY3H5T25sYLtrvQmHdLQbPt2RW37jXd0uT0ocJUebK8t5zL5WzXD79bUAvTX7JblcVGqDh5wnu85S21Pb_ilQp23Qvcqhu4y16zFepKhe5IaPE_vC-RAcwDAAA.png"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q8</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:40.390Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q8</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q9.report.json</t>
+  </si>
+  <si>
+    <t>{"cards/q9-suv.png":"https://mediaservice.audi.com/media/fast/v3_1vzloG1tIiBKdppzWfxH2wcIQ-YGBgqChgYGE4wMBfkpTMCWSlMnJm5iemp-kC-OH9aTmV-aUmxvpGBkbluoSU_IztUhB2olJGH4dPkY46s-6KbtFgT_-lEnzY4KnLkFAMryJzrQILZFUjw6wAJjnYGMAmSiQYRxSA-kxEzAwNrBZARyQACfHylRTkFiUWJuXopqUml6YIaBkQCYXYX1xBHT59gAGx0n1DjAAAA"}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/q9</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:16:45.012Z</t>
+  </si>
+  <si>
+    <t>https://www.audi.de/de/neuwagen/?bycarlinegroup=q9</t>
+  </si>
+  <si>
     <t>language-masters/de/neuwagen/a2-e-tron/a2-e-tron.report.json</t>
   </si>
   <si>
@@ -292,13 +609,31 @@
     <t>2026-10-27T17:21:47.307Z</t>
   </si>
   <si>
+    <t>language-masters/de/neuwagen/fragments/model-filter.report.json</t>
+  </si>
+  <si>
+    <t>["model-filter"]</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>language-masters/de/neuwagen/fragments/model-filter</t>
+  </si>
+  <si>
+    <t>2026-10-27T20:22:42.327Z</t>
+  </si>
+  <si>
+    <t>model-filter fragment</t>
+  </si>
+  <si>
     <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid.report.json</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-sportback-e-hybrid</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:09.364Z</t>
+    <t>2026-10-28T14:03:37.504Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-sportback.report.json</t>
@@ -307,7 +642,7 @@
     <t>language-masters/de/neuwagen/q5/q5-sportback</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:04.513Z</t>
+    <t>2026-10-28T14:03:32.765Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid.report.json</t>
@@ -316,7 +651,7 @@
     <t>language-masters/de/neuwagen/q5/q5-suv-e-hybrid</t>
   </si>
   <si>
-    <t>2026-10-27T17:22:00.558Z</t>
+    <t>2026-10-28T14:03:28.464Z</t>
   </si>
   <si>
     <t>language-masters/de/neuwagen/q5/q5-suv.report.json</t>
@@ -325,7 +660,7 @@
     <t>language-masters/de/neuwagen/q5/q5-suv</t>
   </si>
   <si>
-    <t>2026-10-27T17:21:56.358Z</t>
+    <t>2026-10-28T14:03:24.267Z</t>
   </si>
 </sst>
 </file>
@@ -714,18 +1049,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,649 +1091,1535 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="L5" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
         <v>52</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="K8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" t="s">
+        <v>84</v>
+      </c>
+      <c r="L12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" t="s">
+        <v>126</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" t="s">
+        <v>146</v>
+      </c>
+      <c r="K24" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>155</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" t="s">
+        <v>156</v>
+      </c>
+      <c r="K26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" t="s">
+        <v>161</v>
+      </c>
+      <c r="K27" t="s">
+        <v>46</v>
+      </c>
+      <c r="L27" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>170</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" t="s">
+        <v>176</v>
+      </c>
+      <c r="K30" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" t="s">
+        <v>181</v>
+      </c>
+      <c r="K31" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" t="s">
+        <v>185</v>
+      </c>
+      <c r="K32" t="s">
         <v>54</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="L32" t="s">
         <v>55</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
         <v>57</v>
       </c>
-      <c r="I9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>187</v>
+      </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" t="s">
+        <v>188</v>
+      </c>
+      <c r="K33" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="L33" t="s">
         <v>61</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" t="s">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
         <v>63</v>
       </c>
-      <c r="I10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" t="s">
+        <v>191</v>
+      </c>
+      <c r="K34" t="s">
         <v>66</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="L34" t="s">
         <v>67</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
         <v>69</v>
       </c>
-      <c r="I11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>193</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" t="s">
+        <v>194</v>
+      </c>
+      <c r="K35" t="s">
         <v>72</v>
       </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="L35" t="s">
         <v>73</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" t="s">
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" t="s">
         <v>75</v>
       </c>
-      <c r="I12" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" t="s">
+        <v>197</v>
+      </c>
+      <c r="K36" t="s">
         <v>78</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13">
+      <c r="L36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37">
         <v>0</v>
       </c>
-      <c r="E13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="G37" t="s">
+        <v>201</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" t="s">
+        <v>202</v>
+      </c>
+      <c r="K37" t="s">
+        <v>203</v>
+      </c>
+      <c r="L37" t="s">
         <v>28</v>
       </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
         <v>81</v>
       </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>205</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" t="s">
+        <v>52</v>
+      </c>
+      <c r="J38" t="s">
+        <v>206</v>
+      </c>
+      <c r="K38" t="s">
         <v>84</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="L38" t="s">
         <v>85</v>
       </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I15" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
         <v>87</v>
       </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" t="s">
+        <v>209</v>
+      </c>
+      <c r="K39" t="s">
         <v>90</v>
       </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="L39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
         <v>49</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="C40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" t="s">
         <v>52</v>
       </c>
-      <c r="J17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="J40" t="s">
+        <v>212</v>
+      </c>
+      <c r="K40" t="s">
         <v>96</v>
       </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="L40" t="s">
         <v>97</v>
       </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
         <v>99</v>
       </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" t="s">
+        <v>215</v>
+      </c>
+      <c r="K41" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="L41" t="s">
         <v>103</v>
       </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" t="s">
-        <v>104</v>
-      </c>
-      <c r="I21" t="s">
-        <v>76</v>
-      </c>
-      <c r="J21" t="s">
-        <v>77</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
